--- a/Fichas/Culto de Nidhogg/Ficha Ligma.xlsx
+++ b/Fichas/Culto de Nidhogg/Ficha Ligma.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12315" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12315"/>
   </bookViews>
   <sheets>
     <sheet name="Ligma" sheetId="1" r:id="rId1"/>
@@ -1013,7 +1013,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="187">
   <si>
     <t>Atributos</t>
   </si>
@@ -1382,6 +1382,9 @@
   </si>
   <si>
     <t>+2 Guerra</t>
+  </si>
+  <si>
+    <t>Livros comuns</t>
   </si>
   <si>
     <t>Capacidade</t>
@@ -1579,11 +1582,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1622,7 +1625,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1633,8 +1636,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1648,24 +1652,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1678,77 +1682,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1764,7 +1700,67 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1775,17 +1771,17 @@
       <charset val="0"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <charset val="0"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1826,7 +1822,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1838,37 +1882,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1886,7 +1960,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1898,37 +1972,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1940,67 +1990,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2547,15 +2543,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -2571,17 +2558,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2603,159 +2586,172 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="42" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="42" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="39" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="39" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="37" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5253,18 +5249,18 @@
       </c>
       <c r="D3" s="27">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="39">
         <f ca="1">SUM(C3:D3)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" s="43" t="s">
         <v>83</v>
       </c>
       <c r="H3" s="44">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="2:5">
@@ -5278,11 +5274,11 @@
       </c>
       <c r="D4" s="29">
         <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E4" s="42">
         <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="2:5">
@@ -5296,11 +5292,11 @@
       </c>
       <c r="D5" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="E5" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" ht="15" spans="2:5">
@@ -5314,11 +5310,11 @@
       </c>
       <c r="D6" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E6" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" ht="14.25" spans="2:5">
@@ -5332,11 +5328,11 @@
       </c>
       <c r="D7" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E7" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" ht="15" spans="2:5">
@@ -5350,11 +5346,11 @@
       </c>
       <c r="D8" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E8" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="14.25" spans="2:5">
@@ -5368,11 +5364,11 @@
       </c>
       <c r="D9" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" ht="15" spans="2:5">
@@ -5386,11 +5382,11 @@
       </c>
       <c r="D10" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E10" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" ht="14.25" spans="2:5">
@@ -5404,11 +5400,11 @@
       </c>
       <c r="D11" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E11" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" ht="15" spans="2:5">
@@ -5440,11 +5436,11 @@
       </c>
       <c r="D13" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E13" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" ht="15" spans="2:5">
@@ -5458,11 +5454,11 @@
       </c>
       <c r="D14" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E14" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="2:5">
@@ -5476,11 +5472,11 @@
       </c>
       <c r="D15" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E15" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" ht="15" spans="2:5">
@@ -5494,11 +5490,11 @@
       </c>
       <c r="D16" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E16" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="2:5">
@@ -5512,11 +5508,11 @@
       </c>
       <c r="D17" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E17" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" ht="15" spans="2:5">
@@ -5530,11 +5526,11 @@
       </c>
       <c r="D18" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E18" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="2:5">
@@ -5548,11 +5544,11 @@
       </c>
       <c r="D19" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E19" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" ht="15" spans="2:5">
@@ -5566,11 +5562,11 @@
       </c>
       <c r="D20" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E20" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:5">
@@ -5584,11 +5580,11 @@
       </c>
       <c r="D21" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E21" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" ht="15" spans="2:5">
@@ -5602,11 +5598,11 @@
       </c>
       <c r="D22" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E22" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" ht="14.25" spans="2:5">
@@ -5620,11 +5616,11 @@
       </c>
       <c r="D23" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="30" spans="2:5">
@@ -5638,11 +5634,11 @@
       </c>
       <c r="D24" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E24" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" ht="14.25" spans="2:5">
@@ -5656,11 +5652,11 @@
       </c>
       <c r="D25" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" ht="30" spans="2:5">
@@ -5674,11 +5670,11 @@
       </c>
       <c r="D26" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E26" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="14.25" spans="2:5">
@@ -5692,11 +5688,11 @@
       </c>
       <c r="D27" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E27" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" ht="15" spans="2:5">
@@ -5710,11 +5706,11 @@
       </c>
       <c r="D28" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E28" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="14.25" spans="2:5">
@@ -5728,11 +5724,11 @@
       </c>
       <c r="D29" s="27">
         <f ca="1" t="shared" si="0"/>
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E29" s="39">
         <f ca="1" t="shared" si="1"/>
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" ht="15" spans="2:5">
@@ -5746,11 +5742,11 @@
       </c>
       <c r="D30" s="29">
         <f ca="1" t="shared" si="0"/>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E30" s="42">
         <f ca="1" t="shared" si="1"/>
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" ht="15" spans="2:5">
@@ -5764,11 +5760,11 @@
       </c>
       <c r="D31" s="49">
         <f ca="1" t="shared" si="0"/>
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E31" s="44">
         <f ca="1" t="shared" si="1"/>
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" ht="14.25"/>
@@ -5789,7 +5785,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:H35"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="23.2833333333333" customWidth="1"/>
@@ -5817,7 +5813,10 @@
       </c>
       <c r="H2" s="36"/>
     </row>
-    <row r="3" ht="14.25" spans="2:8">
+    <row r="3" ht="14.25" spans="1:8">
+      <c r="A3">
+        <v>1</v>
+      </c>
       <c r="B3" s="68" t="s">
         <v>88</v>
       </c>
@@ -5838,7 +5837,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:8">
+    <row r="4" ht="15" spans="1:8">
+      <c r="A4">
+        <v>1</v>
+      </c>
       <c r="B4" s="30" t="s">
         <v>90</v>
       </c>
@@ -5859,7 +5861,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="2:8">
+    <row r="5" ht="14.25" spans="1:8">
+      <c r="A5">
+        <v>1</v>
+      </c>
       <c r="B5" s="68" t="s">
         <v>91</v>
       </c>
@@ -5880,7 +5885,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="2:8">
+    <row r="6" ht="15" spans="1:8">
+      <c r="A6">
+        <v>2</v>
+      </c>
       <c r="B6" s="30" t="s">
         <v>93</v>
       </c>
@@ -5901,7 +5909,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="2:8">
+    <row r="7" ht="15" spans="1:8">
+      <c r="A7">
+        <v>3</v>
+      </c>
       <c r="B7" s="68" t="s">
         <v>94</v>
       </c>
@@ -5922,7 +5933,10 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="2:5">
+    <row r="8" ht="15.75" spans="1:5">
+      <c r="A8">
+        <v>4</v>
+      </c>
       <c r="B8" s="30" t="s">
         <v>95</v>
       </c>
@@ -5937,7 +5951,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="2:5">
+    <row r="9" ht="14.25" spans="1:5">
+      <c r="A9">
+        <v>5</v>
+      </c>
       <c r="B9" s="68" t="s">
         <v>96</v>
       </c>
@@ -5952,7 +5969,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="2:5">
+    <row r="10" ht="15" spans="1:5">
+      <c r="A10">
+        <v>6</v>
+      </c>
       <c r="B10" s="30" t="s">
         <v>97</v>
       </c>
@@ -5967,7 +5987,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="2:5">
+    <row r="11" ht="14.25" spans="1:5">
+      <c r="A11">
+        <v>7</v>
+      </c>
       <c r="B11" s="68" t="s">
         <v>98</v>
       </c>
@@ -5982,7 +6005,10 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="2:5">
+    <row r="12" ht="15" spans="1:5">
+      <c r="A12">
+        <v>8</v>
+      </c>
       <c r="B12" s="30" t="s">
         <v>99</v>
       </c>
@@ -5997,7 +6023,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="2:5">
+    <row r="13" ht="14.25" spans="1:5">
+      <c r="A13">
+        <v>9</v>
+      </c>
       <c r="B13" s="68" t="s">
         <v>100</v>
       </c>
@@ -6012,7 +6041,10 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" ht="15" spans="2:5">
+    <row r="14" ht="15" spans="1:5">
+      <c r="A14">
+        <v>10</v>
+      </c>
       <c r="B14" s="30" t="s">
         <v>101</v>
       </c>
@@ -6027,7 +6059,10 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="2:5">
+    <row r="15" ht="14.25" spans="1:5">
+      <c r="A15">
+        <v>10</v>
+      </c>
       <c r="B15" s="68" t="s">
         <v>102</v>
       </c>
@@ -6464,19 +6499,25 @@
       </c>
     </row>
     <row r="18" ht="14.25" spans="2:9">
-      <c r="B18" s="38"/>
+      <c r="B18" s="38" t="s">
+        <v>123</v>
+      </c>
       <c r="C18" s="55"/>
       <c r="D18" s="55"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
+      <c r="E18" s="27">
+        <v>3</v>
+      </c>
+      <c r="F18" s="27">
+        <v>0.1</v>
+      </c>
       <c r="G18" s="27">
         <f t="shared" ref="G18:G21" si="0">PRODUCT(E18:F18)</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="H18" s="27"/>
       <c r="I18" s="39">
         <f t="shared" ref="I18:I21" si="1">PRODUCT(H18,E18)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" ht="15" spans="2:9">
@@ -6530,11 +6571,11 @@
     <row r="22" ht="15"/>
     <row r="23" ht="15.75" spans="2:4">
       <c r="B23" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C23" s="57">
         <f>SUM(G17:G21,F9:F13,F4:F5)</f>
-        <v>13.1</v>
+        <v>13.4</v>
       </c>
       <c r="D23" s="2">
         <f>Ligma!C3*3</f>
@@ -6543,7 +6584,7 @@
     </row>
     <row r="24" ht="14.25" spans="2:4">
       <c r="B24" s="58" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C24" s="59">
         <f>Ligma!C3*10</f>
@@ -6553,7 +6594,7 @@
     </row>
     <row r="25" ht="15.75" spans="2:4">
       <c r="B25" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C25" s="61" t="str">
         <f>IF(C23&gt;D23,"Sobrecarga","Sem Penalidade")</f>
@@ -6606,19 +6647,19 @@
     <row r="1" ht="14.25"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -6627,31 +6668,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>82</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P2" s="36"/>
     </row>
     <row r="3" ht="14.25" spans="2:16">
       <c r="B3" s="26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -6673,13 +6714,13 @@
         <v>8</v>
       </c>
       <c r="K3" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L3" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M3" s="37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -6690,10 +6731,10 @@
     </row>
     <row r="4" ht="15" spans="2:16">
       <c r="B4" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -6715,13 +6756,13 @@
         <v>7</v>
       </c>
       <c r="K4" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L4" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M4" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="M4" s="40" t="s">
-        <v>138</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>60</v>
@@ -6732,10 +6773,10 @@
     </row>
     <row r="5" ht="15" spans="2:16">
       <c r="B5" s="26" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -6757,13 +6798,13 @@
         <v>8</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O5" s="43" t="s">
         <v>74</v>
@@ -6774,10 +6815,10 @@
     </row>
     <row r="6" ht="16.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -6799,21 +6840,21 @@
         <v>7</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -6835,25 +6876,25 @@
         <v>8</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O7" s="35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P7" s="36"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="2:16">
       <c r="B8" s="28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -6875,13 +6916,13 @@
         <v>15</v>
       </c>
       <c r="K8" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M8" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>138</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -6893,10 +6934,10 @@
     </row>
     <row r="9" ht="15" spans="2:16">
       <c r="B9" s="26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -6918,13 +6959,13 @@
         <v>13</v>
       </c>
       <c r="K9" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L9" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="L9" s="27" t="s">
-        <v>138</v>
-      </c>
       <c r="M9" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -6936,10 +6977,10 @@
     </row>
     <row r="10" ht="15" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -6961,13 +7002,13 @@
         <v>7</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -6979,10 +7020,10 @@
     </row>
     <row r="11" ht="15" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7004,13 +7045,13 @@
         <v>7</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -7022,10 +7063,10 @@
     </row>
     <row r="12" ht="15" spans="2:16">
       <c r="B12" s="28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7047,13 +7088,13 @@
         <v>6</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M12" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -7065,10 +7106,10 @@
     </row>
     <row r="13" ht="15.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7090,13 +7131,13 @@
         <v>8</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -7108,10 +7149,10 @@
     </row>
     <row r="14" ht="15.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7135,21 +7176,21 @@
         <v>17</v>
       </c>
       <c r="K14" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M14" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M14" s="40" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7171,21 +7212,21 @@
         <v>8</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" ht="15" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7207,21 +7248,21 @@
         <v>7</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M16" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="2:13">
       <c r="B17" s="26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7243,21 +7284,21 @@
         <v>9</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M17" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" ht="15" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7279,21 +7320,21 @@
         <v>15</v>
       </c>
       <c r="K18" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L18" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="L18" s="29" t="s">
-        <v>138</v>
-      </c>
       <c r="M18" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7315,21 +7356,21 @@
         <v>7</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L19" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="M19" s="37" t="s">
         <v>139</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20" ht="15" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7351,13 +7392,13 @@
         <v>8</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:13">
@@ -7365,7 +7406,7 @@
         <v>83</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7387,21 +7428,21 @@
         <v>12</v>
       </c>
       <c r="K21" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L21" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="L21" s="27" t="s">
-        <v>138</v>
-      </c>
       <c r="M21" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" ht="15" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7425,21 +7466,21 @@
         <v>17</v>
       </c>
       <c r="K22" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L22" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M22" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M22" s="40" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="23" ht="14.25" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7461,21 +7502,21 @@
         <v>11</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L23" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="M23" s="37" t="s">
         <v>139</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="24" ht="15" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7497,21 +7538,21 @@
         <v>15</v>
       </c>
       <c r="K24" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L24" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M24" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M24" s="40" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="25" ht="14.25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7533,21 +7574,21 @@
         <v>15</v>
       </c>
       <c r="K25" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L25" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="M25" s="37" t="s">
         <v>139</v>
-      </c>
-      <c r="L25" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="M25" s="37" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="26" ht="15" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7569,21 +7610,21 @@
         <v>15</v>
       </c>
       <c r="K26" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L26" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M26" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M26" s="40" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="27" ht="14.25" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7607,21 +7648,21 @@
         <v>15</v>
       </c>
       <c r="K27" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L27" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="L27" s="27" t="s">
-        <v>138</v>
-      </c>
       <c r="M27" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" ht="15" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7643,21 +7684,21 @@
         <v>8</v>
       </c>
       <c r="K28" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L28" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M28" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="29" ht="14.25" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7679,21 +7720,21 @@
         <v>8</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" ht="15" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7715,21 +7756,21 @@
         <v>12</v>
       </c>
       <c r="K30" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L30" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="L30" s="29" t="s">
-        <v>138</v>
-      </c>
       <c r="M30" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" ht="14.25" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7751,21 +7792,21 @@
         <v>13</v>
       </c>
       <c r="K31" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L31" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="M31" s="37" t="s">
         <v>139</v>
-      </c>
-      <c r="L31" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="32" ht="15" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7787,21 +7828,21 @@
         <v>9</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" ht="14.25" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7823,13 +7864,13 @@
         <v>13</v>
       </c>
       <c r="K33" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="L33" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="L33" s="32" t="s">
-        <v>138</v>
-      </c>
       <c r="M33" s="47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -7870,19 +7911,19 @@
     <row r="1" ht="14.25"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
       <c r="B2" s="24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="25" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G2" s="25" t="s">
         <v>41</v>
@@ -7891,31 +7932,31 @@
         <v>24</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J2" s="25" t="s">
         <v>82</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L2" s="33" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M2" s="34" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O2" s="35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P2" s="36"/>
     </row>
     <row r="3" ht="14.25" spans="2:16">
       <c r="B3" s="26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D3" s="27">
         <f>VLOOKUP(C3,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7937,13 +7978,13 @@
         <v>8</v>
       </c>
       <c r="K3" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L3" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M3" s="37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O3" s="38" t="s">
         <v>34</v>
@@ -7954,10 +7995,10 @@
     </row>
     <row r="4" ht="15" spans="2:16">
       <c r="B4" s="28" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D4" s="29">
         <f>VLOOKUP(C4,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -7979,13 +8020,13 @@
         <v>7</v>
       </c>
       <c r="K4" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L4" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M4" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="M4" s="40" t="s">
-        <v>138</v>
       </c>
       <c r="O4" s="41" t="s">
         <v>60</v>
@@ -7996,10 +8037,10 @@
     </row>
     <row r="5" ht="15" spans="2:16">
       <c r="B5" s="26" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D5" s="27">
         <f>VLOOKUP(C5,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8021,13 +8062,13 @@
         <v>8</v>
       </c>
       <c r="K5" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M5" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O5" s="43" t="s">
         <v>74</v>
@@ -8038,10 +8079,10 @@
     </row>
     <row r="6" ht="16.5" spans="2:13">
       <c r="B6" s="28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D6" s="29">
         <f>VLOOKUP(C6,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8063,21 +8104,21 @@
         <v>7</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M6" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
       <c r="B7" s="26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D7" s="27">
         <f>VLOOKUP(C7,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8099,25 +8140,25 @@
         <v>8</v>
       </c>
       <c r="K7" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L7" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M7" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O7" s="35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P7" s="36"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="2:16">
       <c r="B8" s="28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D8" s="29">
         <f>VLOOKUP(C8,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8139,13 +8180,13 @@
         <v>15</v>
       </c>
       <c r="K8" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L8" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M8" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>138</v>
       </c>
       <c r="O8" s="38" t="s">
         <v>4</v>
@@ -8157,10 +8198,10 @@
     </row>
     <row r="9" ht="15" spans="2:16">
       <c r="B9" s="26" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D9" s="27">
         <f>VLOOKUP(C9,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8182,13 +8223,13 @@
         <v>13</v>
       </c>
       <c r="K9" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L9" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="L9" s="27" t="s">
-        <v>138</v>
-      </c>
       <c r="M9" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O9" s="41" t="s">
         <v>9</v>
@@ -8200,10 +8241,10 @@
     </row>
     <row r="10" ht="15" spans="2:16">
       <c r="B10" s="28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D10" s="29">
         <f>VLOOKUP(C10,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8225,13 +8266,13 @@
         <v>7</v>
       </c>
       <c r="K10" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L10" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M10" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O10" s="38" t="s">
         <v>10</v>
@@ -8243,10 +8284,10 @@
     </row>
     <row r="11" ht="15" spans="2:16">
       <c r="B11" s="26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D11" s="27">
         <f>VLOOKUP(C11,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8268,13 +8309,13 @@
         <v>7</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L11" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O11" s="41" t="s">
         <v>12</v>
@@ -8286,10 +8327,10 @@
     </row>
     <row r="12" ht="15" spans="2:16">
       <c r="B12" s="28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D12" s="29">
         <f>VLOOKUP(C12,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8311,13 +8352,13 @@
         <v>6</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L12" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M12" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O12" s="38" t="s">
         <v>14</v>
@@ -8329,10 +8370,10 @@
     </row>
     <row r="13" ht="15.75" spans="2:16">
       <c r="B13" s="26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D13" s="27">
         <f>VLOOKUP(C13,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8354,13 +8395,13 @@
         <v>8</v>
       </c>
       <c r="K13" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L13" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M13" s="37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O13" s="45" t="s">
         <v>16</v>
@@ -8372,10 +8413,10 @@
     </row>
     <row r="14" ht="15.75" spans="2:13">
       <c r="B14" s="28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D14" s="29">
         <f>VLOOKUP(C14,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8399,21 +8440,21 @@
         <v>16</v>
       </c>
       <c r="K14" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L14" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M14" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="L14" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M14" s="40" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="2:13">
       <c r="B15" s="26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D15" s="27">
         <f>VLOOKUP(C15,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8435,21 +8476,21 @@
         <v>8</v>
       </c>
       <c r="K15" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L15" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M15" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" ht="15" spans="2:13">
       <c r="B16" s="28" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D16" s="29">
         <f>VLOOKUP(C16,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8471,21 +8512,21 @@
         <v>7</v>
       </c>
       <c r="K16" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L16" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M16" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="2:13">
       <c r="B17" s="26" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D17" s="27">
         <f>VLOOKUP(C17,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8507,21 +8548,21 @@
         <v>9</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L17" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M17" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" ht="15" spans="2:13">
       <c r="B18" s="28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D18" s="29">
         <f>VLOOKUP(C18,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8543,21 +8584,21 @@
         <v>15</v>
       </c>
       <c r="K18" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L18" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="L18" s="29" t="s">
-        <v>138</v>
-      </c>
       <c r="M18" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="2:13">
       <c r="B19" s="26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D19" s="27">
         <f>VLOOKUP(C19,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8579,21 +8620,21 @@
         <v>7</v>
       </c>
       <c r="K19" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L19" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="M19" s="37" t="s">
         <v>139</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20" ht="15" spans="2:13">
       <c r="B20" s="28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D20" s="29">
         <f>VLOOKUP(C20,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8615,13 +8656,13 @@
         <v>8</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L20" s="29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M20" s="40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:13">
@@ -8629,7 +8670,7 @@
         <v>83</v>
       </c>
       <c r="C21" s="27" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D21" s="27">
         <f>VLOOKUP(C21,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8651,21 +8692,21 @@
         <v>12</v>
       </c>
       <c r="K21" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L21" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="L21" s="27" t="s">
-        <v>138</v>
-      </c>
       <c r="M21" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" ht="15" spans="2:13">
       <c r="B22" s="28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D22" s="29">
         <f>VLOOKUP(C22,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8689,21 +8730,21 @@
         <v>17</v>
       </c>
       <c r="K22" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L22" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M22" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M22" s="40" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="23" ht="14.25" spans="2:13">
       <c r="B23" s="26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D23" s="27">
         <f>VLOOKUP(C23,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8725,21 +8766,21 @@
         <v>11</v>
       </c>
       <c r="K23" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L23" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="M23" s="37" t="s">
         <v>139</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="24" ht="15" spans="2:13">
       <c r="B24" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D24" s="29">
         <f>VLOOKUP(C24,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8761,21 +8802,21 @@
         <v>15</v>
       </c>
       <c r="K24" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L24" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M24" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M24" s="40" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="25" ht="14.25" spans="2:13">
       <c r="B25" s="26" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C25" s="27" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D25" s="27">
         <f>VLOOKUP(C25,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8797,21 +8838,21 @@
         <v>15</v>
       </c>
       <c r="K25" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L25" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="M25" s="37" t="s">
         <v>139</v>
-      </c>
-      <c r="L25" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="M25" s="37" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="26" ht="15" spans="2:13">
       <c r="B26" s="30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D26" s="29">
         <f>VLOOKUP(C26,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8833,21 +8874,21 @@
         <v>15</v>
       </c>
       <c r="K26" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L26" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M26" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M26" s="40" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="27" ht="14.25" spans="2:13">
       <c r="B27" s="26" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D27" s="27">
         <f>VLOOKUP(C27,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8871,21 +8912,21 @@
         <v>15</v>
       </c>
       <c r="K27" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L27" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="L27" s="27" t="s">
-        <v>138</v>
-      </c>
       <c r="M27" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" ht="15" spans="2:13">
       <c r="B28" s="28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C28" s="29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D28" s="29">
         <f>VLOOKUP(C28,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8907,21 +8948,21 @@
         <v>8</v>
       </c>
       <c r="K28" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L28" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="M28" s="40" t="s">
         <v>139</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="29" ht="14.25" spans="2:13">
       <c r="B29" s="26" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C29" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D29" s="27">
         <f>VLOOKUP(C29,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8943,21 +8984,21 @@
         <v>8</v>
       </c>
       <c r="K29" s="27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L29" s="27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" ht="15" spans="2:13">
       <c r="B30" s="28" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C30" s="29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D30" s="29">
         <f>VLOOKUP(C30,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -8979,21 +9020,21 @@
         <v>12</v>
       </c>
       <c r="K30" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="L30" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="L30" s="29" t="s">
-        <v>138</v>
-      </c>
       <c r="M30" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" ht="14.25" spans="2:13">
       <c r="B31" s="26" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C31" s="27" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D31" s="27">
         <f>VLOOKUP(C31,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -9015,21 +9056,21 @@
         <v>13</v>
       </c>
       <c r="K31" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="L31" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="M31" s="37" t="s">
         <v>139</v>
-      </c>
-      <c r="L31" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="32" ht="15" spans="2:13">
       <c r="B32" s="28" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C32" s="29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D32" s="29">
         <f>VLOOKUP(C32,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -9051,21 +9092,21 @@
         <v>9</v>
       </c>
       <c r="K32" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L32" s="29" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M32" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" ht="14.25" spans="2:13">
       <c r="B33" s="31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D33" s="32">
         <f>VLOOKUP(C33,Ligma!$B$3:$D$8,3,FALSE)</f>
@@ -9087,13 +9128,13 @@
         <v>13</v>
       </c>
       <c r="K33" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="L33" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="L33" s="32" t="s">
-        <v>138</v>
-      </c>
       <c r="M33" s="47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -9126,7 +9167,7 @@
     <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:13">
       <c r="B2" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C2" s="2"/>
       <c r="E2" s="1">
@@ -9136,16 +9177,16 @@
         <v>2</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M2" s="2">
         <f>12+Ligma!D5</f>
@@ -9176,7 +9217,7 @@
         <v>0</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M3" s="4">
         <v>4</v>
@@ -9206,7 +9247,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M4" s="8">
         <v>1</v>
@@ -9322,7 +9363,7 @@
     </row>
     <row r="12" ht="15.75" spans="2:10">
       <c r="B12" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C12" s="2">
         <f>3+Ligma!D5</f>
@@ -9341,7 +9382,7 @@
     </row>
     <row r="13" ht="14.25" spans="2:10">
       <c r="B13" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(M3:M4)</f>
@@ -9386,13 +9427,13 @@
     </row>
     <row r="16" ht="15.75" spans="2:10">
       <c r="B16" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>82</v>

--- a/Fichas/Culto de Nidhogg/Ficha Ligma.xlsx
+++ b/Fichas/Culto de Nidhogg/Ficha Ligma.xlsx
@@ -985,7 +985,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Arial"/>
-            <charset val="0"/>
+            <charset val="134"/>
           </rPr>
           <t>dopanime:</t>
         </r>
@@ -993,7 +993,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Arial"/>
-            <charset val="0"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 Machado de guerra:
@@ -1013,7 +1013,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="188">
   <si>
     <t>Atributos</t>
   </si>
@@ -1550,6 +1550,9 @@
   </si>
   <si>
     <t>Nível de Personagem</t>
+  </si>
+  <si>
+    <t>Bônus em Perícias Treinadas</t>
   </si>
   <si>
     <t>Bônus em Perícias</t>
@@ -1581,10 +1584,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="29">
     <font>
@@ -1629,16 +1632,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1660,6 +1671,73 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -1669,14 +1747,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1692,89 +1763,10 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="Aptos Narrow"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <charset val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1785,7 +1777,18 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1822,145 +1825,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1978,13 +1843,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1997,6 +1916,90 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2145,6 +2148,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -2224,19 +2266,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -2278,19 +2307,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thick">
         <color auto="1"/>
@@ -2299,19 +2315,6 @@
         <color auto="1"/>
       </top>
       <bottom style="thick">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thick">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -2510,11 +2513,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2560,11 +2569,29 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2583,179 +2610,155 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="37" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="39" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="42" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="39" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2820,153 +2823,165 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3018,10 +3033,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4361,424 +4376,424 @@
   <dimension ref="B1:N41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="12.425" customWidth="1"/>
-    <col min="3" max="3" width="6.14166666666667" customWidth="1"/>
-    <col min="4" max="4" width="13.2833333333333" customWidth="1"/>
-    <col min="6" max="6" width="14.5666666666667" customWidth="1"/>
-    <col min="7" max="8" width="7.85833333333333" customWidth="1"/>
+    <col min="2" max="2" width="12.375" customWidth="1"/>
+    <col min="3" max="3" width="6.125" customWidth="1"/>
+    <col min="4" max="4" width="13.25" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="8" width="7.875" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="14" max="14" width="36.425" customWidth="1"/>
+    <col min="14" max="14" width="36.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" customHeight="1" spans="2:14">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="36" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="48">
+      <c r="G2" s="52">
         <f>VLOOKUP(G10,'uns dados aí'!$H$2:$I$22,2,TRUE)</f>
         <v>10</v>
       </c>
-      <c r="H2" s="36"/>
-      <c r="K2" s="35" t="s">
+      <c r="H2" s="40"/>
+      <c r="K2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="48"/>
-      <c r="M2" s="48"/>
-      <c r="N2" s="36"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="40"/>
     </row>
     <row r="3" ht="14.25" spans="2:14">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="31">
         <f>'uns dados aí'!C3+(VLOOKUP(B3,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>16</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="43">
         <f t="shared" ref="D3:D8" si="0">ROUNDDOWN((C3-10)/2,0)</f>
         <v>3</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="27">
+      <c r="G3" s="31">
         <f>H3-L25-SUM(L4:L22)</f>
         <v>49</v>
       </c>
-      <c r="H3" s="39">
-        <f>'uns dados aí'!M2+((G2-1)*'uns dados aí'!C12)</f>
+      <c r="H3" s="43">
+        <f>'uns dados aí'!N2+((G2-1)*'uns dados aí'!C12)</f>
         <v>49</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="39" t="s">
+      <c r="N3" s="43" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:14">
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="33">
         <f>'uns dados aí'!C4+(VLOOKUP(B4,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>17</v>
       </c>
-      <c r="D4" s="42">
+      <c r="D4" s="46">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="29">
+      <c r="G4" s="33">
         <f>H4-L26-SUM(M4:M22)</f>
         <v>50</v>
       </c>
-      <c r="H4" s="42">
+      <c r="H4" s="46">
         <f>'uns dados aí'!C13*G2</f>
         <v>50</v>
       </c>
-      <c r="K4" s="41">
+      <c r="K4" s="45">
         <v>1</v>
       </c>
-      <c r="L4" s="29"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="42"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="46"/>
     </row>
     <row r="5" ht="14.25" spans="2:14">
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="31">
         <f>'uns dados aí'!C5+(VLOOKUP(B5,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>13</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="43">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="F5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="37">
+      <c r="G5" s="41">
         <f>10+D4+C16</f>
         <v>15</v>
       </c>
-      <c r="H5" s="88"/>
-      <c r="K5" s="38">
+      <c r="H5" s="92"/>
+      <c r="K5" s="42">
         <v>2</v>
       </c>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="39"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="43"/>
     </row>
     <row r="6" ht="15" spans="2:14">
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="33">
         <f>'uns dados aí'!C6+(VLOOKUP(B6,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>22</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="46">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="44">
         <f>G5+Perícias!J12</f>
         <v>21</v>
       </c>
-      <c r="H6" s="89"/>
-      <c r="K6" s="41">
+      <c r="H6" s="93"/>
+      <c r="K6" s="45">
         <v>3</v>
       </c>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="42"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="46"/>
     </row>
     <row r="7" ht="14.25" spans="2:14">
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="31">
         <f>'uns dados aí'!C7+(VLOOKUP(B7,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>18</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="41">
         <f>Perícias!J27+Perícias!J21</f>
-        <v>27</v>
-      </c>
-      <c r="H7" s="88"/>
-      <c r="K7" s="38">
+        <v>37</v>
+      </c>
+      <c r="H7" s="92"/>
+      <c r="K7" s="42">
         <v>4</v>
       </c>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="39"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="43"/>
     </row>
     <row r="8" ht="15.75" spans="2:14">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="52">
+      <c r="C8" s="56">
         <f>'uns dados aí'!C8+(VLOOKUP(B8,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>14</v>
       </c>
-      <c r="D8" s="46">
+      <c r="D8" s="50">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="90">
+      <c r="G8" s="94">
         <v>0.5</v>
       </c>
-      <c r="H8" s="91"/>
-      <c r="K8" s="41">
+      <c r="H8" s="95"/>
+      <c r="K8" s="45">
         <v>5</v>
       </c>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="42"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="46"/>
     </row>
     <row r="9" ht="15" spans="6:14">
-      <c r="F9" s="38" t="s">
+      <c r="F9" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="39"/>
-      <c r="K9" s="38">
+      <c r="G9" s="31"/>
+      <c r="H9" s="43"/>
+      <c r="K9" s="42">
         <v>6</v>
       </c>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="39"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="43"/>
     </row>
     <row r="10" ht="15.75" spans="6:14">
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="52">
+      <c r="G10" s="56">
         <v>45000</v>
       </c>
-      <c r="H10" s="46"/>
-      <c r="K10" s="41">
+      <c r="H10" s="50"/>
+      <c r="K10" s="45">
         <v>7</v>
       </c>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="42"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="46"/>
     </row>
     <row r="11" ht="15.75" spans="11:14">
-      <c r="K11" s="38">
+      <c r="K11" s="42">
         <v>8</v>
       </c>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="39"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="43"/>
     </row>
     <row r="12" ht="16.5" spans="2:14">
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="73"/>
-      <c r="K12" s="41">
+      <c r="C12" s="76"/>
+      <c r="D12" s="76"/>
+      <c r="E12" s="76"/>
+      <c r="F12" s="76"/>
+      <c r="G12" s="76"/>
+      <c r="H12" s="76"/>
+      <c r="I12" s="77"/>
+      <c r="K12" s="45">
         <v>9</v>
       </c>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="N12" s="42"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="46"/>
     </row>
     <row r="13" ht="15.75" spans="2:14">
-      <c r="B13" s="87"/>
-      <c r="K13" s="38">
+      <c r="B13" s="91"/>
+      <c r="K13" s="42">
         <v>10</v>
       </c>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="39"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="43"/>
     </row>
     <row r="14" ht="15.75" spans="2:14">
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="48"/>
-      <c r="D14" s="36"/>
-      <c r="F14" s="35" t="s">
+      <c r="C14" s="52"/>
+      <c r="D14" s="40"/>
+      <c r="F14" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="48"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="36"/>
-      <c r="K14" s="41">
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="40"/>
+      <c r="K14" s="45">
         <v>11</v>
       </c>
-      <c r="L14" s="29"/>
-      <c r="M14" s="29"/>
-      <c r="N14" s="42"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="46"/>
     </row>
     <row r="15" ht="14.25" spans="2:14">
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="38" t="s">
+      <c r="F15" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="G15" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="H15" s="27" t="s">
+      <c r="H15" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="39" t="s">
+      <c r="I15" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="K15" s="38">
+      <c r="K15" s="42">
         <v>12</v>
       </c>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="39"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="31"/>
+      <c r="N15" s="43"/>
     </row>
     <row r="16" ht="30.75" spans="2:14">
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="52">
+      <c r="C16" s="56">
         <f>IFERROR(VLOOKUP($B$16,Inventário!$B$3:$E$5,2,FALSE),"")</f>
         <v>2</v>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="50">
         <f>IFERROR(VLOOKUP($B$16,Inventário!$B$3:$E$5,3,FALSE),"")</f>
         <v>0</v>
       </c>
-      <c r="F16" s="45" t="s">
+      <c r="F16" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="52" t="str">
+      <c r="G16" s="56" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$E$13,2,FALSE),"")</f>
         <v>3d6+2</v>
       </c>
-      <c r="H16" s="52" t="str">
+      <c r="H16" s="56" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$E$13,3,FALSE),"")</f>
         <v>Abrir nota</v>
       </c>
-      <c r="I16" s="46" t="str">
+      <c r="I16" s="50" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$H$13,7,FALSE),"")</f>
         <v>x4</v>
       </c>
-      <c r="K16" s="41">
+      <c r="K16" s="45">
         <v>13</v>
       </c>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="42"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="46"/>
     </row>
     <row r="17" ht="15" spans="11:14">
-      <c r="K17" s="38">
+      <c r="K17" s="42">
         <v>14</v>
       </c>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="39"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="43"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="11:14">
-      <c r="K18" s="41">
+      <c r="K18" s="45">
         <v>15</v>
       </c>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="42"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="46"/>
     </row>
     <row r="19" ht="14.25" spans="11:14">
-      <c r="K19" s="38">
+      <c r="K19" s="42">
         <v>16</v>
       </c>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="39"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="31"/>
+      <c r="N19" s="43"/>
     </row>
     <row r="20" ht="15" spans="11:14">
-      <c r="K20" s="41">
+      <c r="K20" s="45">
         <v>17</v>
       </c>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="42"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="46"/>
     </row>
     <row r="21" ht="14.25" spans="11:14">
-      <c r="K21" s="38">
+      <c r="K21" s="42">
         <v>18</v>
       </c>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="39"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="31"/>
+      <c r="N21" s="43"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="11:14">
-      <c r="K22" s="45">
+      <c r="K22" s="49">
         <v>20</v>
       </c>
-      <c r="L22" s="52"/>
-      <c r="M22" s="52"/>
-      <c r="N22" s="46"/>
+      <c r="L22" s="56"/>
+      <c r="M22" s="56"/>
+      <c r="N22" s="50"/>
     </row>
     <row r="23" ht="15"/>
     <row r="24" ht="15.75" spans="11:12">
-      <c r="K24" s="35" t="s">
+      <c r="K24" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="L24" s="36"/>
+      <c r="L24" s="40"/>
     </row>
     <row r="25" ht="14.25" spans="11:12">
-      <c r="K25" s="38" t="s">
+      <c r="K25" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="L25" s="39"/>
+      <c r="L25" s="43"/>
     </row>
     <row r="26" ht="15.75" spans="11:12">
-      <c r="K26" s="45" t="s">
+      <c r="K26" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="L26" s="46"/>
+      <c r="L26" s="50"/>
     </row>
     <row r="27" ht="14.25"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -4817,345 +4832,345 @@
   <dimension ref="A1:O23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="12" max="12" width="19.7083333333333" customWidth="1"/>
+    <col min="12" max="12" width="19.75" customWidth="1"/>
     <col min="13" max="13" width="22.25" customWidth="1"/>
-    <col min="14" max="14" width="12.1416666666667" customWidth="1"/>
+    <col min="14" max="14" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.5" spans="1:15">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="73"/>
-      <c r="I1" s="71" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="77"/>
+      <c r="I1" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
-      <c r="L1" s="72"/>
-      <c r="M1" s="72"/>
-      <c r="N1" s="72"/>
-      <c r="O1" s="73"/>
+      <c r="J1" s="76"/>
+      <c r="K1" s="76"/>
+      <c r="L1" s="76"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="77"/>
     </row>
     <row r="2" ht="15"/>
     <row r="3" ht="15.75" spans="2:13">
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48" t="s">
+      <c r="C3" s="52"/>
+      <c r="D3" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="36"/>
-      <c r="K3" s="74" t="s">
+      <c r="E3" s="52"/>
+      <c r="F3" s="40"/>
+      <c r="K3" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="75" t="s">
+      <c r="L3" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="83" t="s">
+      <c r="M3" s="87" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="2:13">
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="27"/>
-      <c r="F4" s="39" t="s">
+      <c r="E4" s="31"/>
+      <c r="F4" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="76" t="s">
+      <c r="K4" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="77" t="s">
+      <c r="L4" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="84" t="s">
+      <c r="M4" s="88" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="2:13">
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29" t="s">
+      <c r="C5" s="33"/>
+      <c r="D5" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="42" t="s">
+      <c r="E5" s="33"/>
+      <c r="F5" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="78" t="s">
+      <c r="K5" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="79" t="s">
+      <c r="L5" s="83" t="s">
         <v>46</v>
       </c>
-      <c r="M5" s="92" t="s">
+      <c r="M5" s="96" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="2:13">
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27" t="s">
+      <c r="C6" s="31"/>
+      <c r="D6" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="27"/>
-      <c r="F6" s="39" t="s">
+      <c r="E6" s="31"/>
+      <c r="F6" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="76" t="s">
+      <c r="K6" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="77" t="s">
+      <c r="L6" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="93" t="s">
+      <c r="M6" s="97" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" ht="15" spans="2:13">
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29" t="s">
+      <c r="C7" s="33"/>
+      <c r="D7" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="42" t="s">
+      <c r="E7" s="33"/>
+      <c r="F7" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="78" t="s">
+      <c r="K7" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="79" t="s">
+      <c r="L7" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="85"/>
+      <c r="M7" s="89"/>
     </row>
     <row r="8" ht="14.25" spans="2:13">
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27" t="s">
+      <c r="C8" s="31"/>
+      <c r="D8" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="27"/>
-      <c r="F8" s="39" t="s">
+      <c r="E8" s="31"/>
+      <c r="F8" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="76" t="s">
+      <c r="K8" s="80" t="s">
         <v>58</v>
       </c>
-      <c r="L8" s="80" t="s">
+      <c r="L8" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="M8" s="84"/>
+      <c r="M8" s="88"/>
     </row>
     <row r="9" ht="15" spans="2:13">
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29" t="s">
+      <c r="C9" s="33"/>
+      <c r="D9" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="42" t="s">
+      <c r="E9" s="33"/>
+      <c r="F9" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="78"/>
-      <c r="L9" s="79"/>
-      <c r="M9" s="85"/>
+      <c r="K9" s="82"/>
+      <c r="L9" s="83"/>
+      <c r="M9" s="89"/>
     </row>
     <row r="10" ht="15" customHeight="1" spans="2:13">
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="42" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27" t="s">
+      <c r="C10" s="31"/>
+      <c r="D10" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="39" t="s">
+      <c r="E10" s="31"/>
+      <c r="F10" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="76"/>
-      <c r="L10" s="77"/>
-      <c r="M10" s="84"/>
+      <c r="K10" s="80"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="88"/>
     </row>
     <row r="11" ht="15" spans="2:13">
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29" t="s">
+      <c r="C11" s="33"/>
+      <c r="D11" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="42" t="s">
+      <c r="E11" s="33"/>
+      <c r="F11" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="78"/>
-      <c r="L11" s="79"/>
-      <c r="M11" s="85"/>
+      <c r="K11" s="82"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="89"/>
     </row>
     <row r="12" ht="14.25" spans="2:13">
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27" t="s">
+      <c r="C12" s="31"/>
+      <c r="D12" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="27"/>
-      <c r="F12" s="39" t="s">
+      <c r="E12" s="31"/>
+      <c r="F12" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="76"/>
-      <c r="L12" s="77"/>
-      <c r="M12" s="84"/>
+      <c r="K12" s="80"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="88"/>
     </row>
     <row r="13" ht="15" spans="2:13">
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29" t="s">
+      <c r="C13" s="33"/>
+      <c r="D13" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="42" t="s">
+      <c r="E13" s="33"/>
+      <c r="F13" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="K13" s="78"/>
-      <c r="L13" s="79"/>
-      <c r="M13" s="85"/>
+      <c r="K13" s="82"/>
+      <c r="L13" s="83"/>
+      <c r="M13" s="89"/>
     </row>
     <row r="14" ht="14.25" spans="2:13">
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="39"/>
-      <c r="K14" s="76"/>
-      <c r="L14" s="77"/>
-      <c r="M14" s="84"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="43"/>
+      <c r="K14" s="80"/>
+      <c r="L14" s="81"/>
+      <c r="M14" s="88"/>
     </row>
     <row r="15" ht="15" spans="2:13">
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="42"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="79"/>
-      <c r="M15" s="85"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="46"/>
+      <c r="K15" s="82"/>
+      <c r="L15" s="83"/>
+      <c r="M15" s="89"/>
     </row>
     <row r="16" ht="14.25" spans="2:13">
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="39"/>
-      <c r="K16" s="76"/>
-      <c r="L16" s="77"/>
-      <c r="M16" s="84"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="43"/>
+      <c r="K16" s="80"/>
+      <c r="L16" s="81"/>
+      <c r="M16" s="88"/>
     </row>
     <row r="17" ht="15" spans="2:13">
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="42"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="79"/>
-      <c r="M17" s="85"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="46"/>
+      <c r="K17" s="82"/>
+      <c r="L17" s="83"/>
+      <c r="M17" s="89"/>
     </row>
     <row r="18" ht="14.25" spans="2:13">
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="39"/>
-      <c r="K18" s="76"/>
-      <c r="L18" s="77"/>
-      <c r="M18" s="84"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="43"/>
+      <c r="K18" s="80"/>
+      <c r="L18" s="81"/>
+      <c r="M18" s="88"/>
     </row>
     <row r="19" ht="15" spans="2:13">
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="42"/>
-      <c r="K19" s="78"/>
-      <c r="L19" s="79"/>
-      <c r="M19" s="85"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="46"/>
+      <c r="K19" s="82"/>
+      <c r="L19" s="83"/>
+      <c r="M19" s="89"/>
     </row>
     <row r="20" ht="14.25" spans="2:13">
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="39"/>
-      <c r="K20" s="76"/>
-      <c r="L20" s="77"/>
-      <c r="M20" s="84"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="43"/>
+      <c r="K20" s="80"/>
+      <c r="L20" s="81"/>
+      <c r="M20" s="88"/>
     </row>
     <row r="21" ht="15" spans="2:13">
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="42"/>
-      <c r="K21" s="78"/>
-      <c r="L21" s="79"/>
-      <c r="M21" s="85"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="46"/>
+      <c r="K21" s="82"/>
+      <c r="L21" s="83"/>
+      <c r="M21" s="89"/>
     </row>
     <row r="22" ht="15" spans="2:13">
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="44"/>
-      <c r="K22" s="81"/>
-      <c r="L22" s="82"/>
-      <c r="M22" s="86"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="53"/>
+      <c r="F22" s="48"/>
+      <c r="K22" s="85"/>
+      <c r="L22" s="86"/>
+      <c r="M22" s="90"/>
     </row>
     <row r="23" ht="14.25"/>
   </sheetData>
@@ -5215,556 +5230,556 @@
   <dimension ref="B1:H32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="13.8583333333333" customWidth="1"/>
-    <col min="7" max="7" width="8.425" customWidth="1"/>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="7" max="7" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:8">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="52" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="50" t="s">
+      <c r="G2" s="54" t="s">
         <v>80</v>
       </c>
-      <c r="H2" s="65"/>
+      <c r="H2" s="69"/>
     </row>
     <row r="3" ht="15" spans="2:8">
-      <c r="B3" s="38" t="str">
+      <c r="B3" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Acrobacia</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="31">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>8</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="31">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>15</v>
-      </c>
-      <c r="E3" s="39">
+        <v>1</v>
+      </c>
+      <c r="E3" s="43">
         <f ca="1">SUM(C3:D3)</f>
-        <v>23</v>
-      </c>
-      <c r="G3" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="H3" s="44">
+      <c r="H3" s="48">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="2:5">
-      <c r="B4" s="41" t="str">
+      <c r="B4" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Adestramento</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>7</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="33">
         <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
-        <v>5</v>
-      </c>
-      <c r="E4" s="42">
+        <v>10</v>
+      </c>
+      <c r="E4" s="46">
         <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" ht="14.25" spans="2:5">
-      <c r="B5" s="38" t="str">
+      <c r="B5" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atletismo</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="31">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>8</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="31">
         <f ca="1" t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E5" s="39">
+        <v>1</v>
+      </c>
+      <c r="E5" s="43">
         <f ca="1" t="shared" si="1"/>
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" ht="15" spans="2:5">
-      <c r="B6" s="41" t="str">
+      <c r="B6" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atuação</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>7</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="E6" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25" spans="2:5">
+      <c r="B7" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Cavalgar</v>
+      </c>
+      <c r="C7" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>8</v>
+      </c>
+      <c r="D7" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="E7" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="2:5">
+      <c r="B8" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Conhecimento</v>
+      </c>
+      <c r="C8" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>20</v>
+      </c>
+      <c r="D8" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E8" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25" spans="2:5">
+      <c r="B9" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Cura</v>
+      </c>
+      <c r="C9" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>18</v>
+      </c>
+      <c r="D9" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="E9" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="2:5">
+      <c r="B10" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Diplomacia</v>
+      </c>
+      <c r="C10" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>7</v>
+      </c>
+      <c r="D10" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="E10" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" ht="14.25" spans="2:5">
+      <c r="B11" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Enganação</v>
+      </c>
+      <c r="C11" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>7</v>
+      </c>
+      <c r="D11" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="E11" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="2:5">
+      <c r="B12" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Fortitude</v>
+      </c>
+      <c r="C12" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>6</v>
+      </c>
+      <c r="D12" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E12" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" ht="14.25" spans="2:5">
+      <c r="B13" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Furtividade</v>
+      </c>
+      <c r="C13" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>8</v>
+      </c>
+      <c r="D13" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E13" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="2:5">
+      <c r="B14" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Guerra</v>
+      </c>
+      <c r="C14" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>22</v>
+      </c>
+      <c r="D14" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E14" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="2:5">
+      <c r="B15" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Iniciativa</v>
+      </c>
+      <c r="C15" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>8</v>
+      </c>
+      <c r="D15" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E15" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="2:5">
+      <c r="B16" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Intimidação</v>
+      </c>
+      <c r="C16" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>7</v>
+      </c>
+      <c r="D16" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="E16" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="2:5">
+      <c r="B17" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Intuição</v>
+      </c>
+      <c r="C17" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>9</v>
+      </c>
+      <c r="D17" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="E17" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="2:5">
+      <c r="B18" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Investigação</v>
+      </c>
+      <c r="C18" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>20</v>
+      </c>
+      <c r="D18" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="E18" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="2:5">
+      <c r="B19" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Jogatina</v>
+      </c>
+      <c r="C19" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>7</v>
+      </c>
+      <c r="D19" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="E19" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="2:5">
+      <c r="B20" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ladinagem</v>
+      </c>
+      <c r="C20" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>8</v>
+      </c>
+      <c r="D20" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E20" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="2:5">
+      <c r="B21" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Luta</v>
+      </c>
+      <c r="C21" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>17</v>
+      </c>
+      <c r="D21" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E21" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="2:5">
+      <c r="B22" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Misticismo</v>
+      </c>
+      <c r="C22" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>22</v>
+      </c>
+      <c r="D22" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E22" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" spans="2:5">
+      <c r="B23" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Nobreza</v>
+      </c>
+      <c r="C23" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>11</v>
+      </c>
+      <c r="D23" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="E23" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" ht="30" spans="2:5">
+      <c r="B24" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ofício (Alquimista)</v>
+      </c>
+      <c r="C24" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>20</v>
+      </c>
+      <c r="D24" s="33">
         <f ca="1" t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E24" s="46">
         <f ca="1" t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" spans="2:5">
-      <c r="B7" s="38" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="2:5">
+      <c r="B25" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Cavalgar</v>
-      </c>
-      <c r="C7" s="27">
+        <v>Ofício (Armeiro)</v>
+      </c>
+      <c r="C25" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>20</v>
+      </c>
+      <c r="D25" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E25" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" ht="30" spans="2:5">
+      <c r="B26" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Ofício (Engenhoqueiro)</v>
+      </c>
+      <c r="C26" s="33">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>20</v>
+      </c>
+      <c r="D26" s="33">
+        <f ca="1" t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E26" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="2:5">
+      <c r="B27" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Percepção</v>
+      </c>
+      <c r="C27" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
+        <v>20</v>
+      </c>
+      <c r="D27" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="E27" s="43">
+        <f ca="1" t="shared" si="1"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="2:5">
+      <c r="B28" s="45" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Pilotagem</v>
+      </c>
+      <c r="C28" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
         <v>8</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D28" s="33">
         <f ca="1" t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="E28" s="46">
+        <f ca="1" t="shared" si="1"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" ht="14.25" spans="2:5">
+      <c r="B29" s="42" t="str">
+        <f>Tabela1[[#This Row],[Perícia]]</f>
+        <v>Pontaria</v>
+      </c>
+      <c r="C29" s="31">
+        <f>Tabela1[[#This Row],[Total]]</f>
         <v>8</v>
       </c>
-      <c r="E7" s="39">
+      <c r="D29" s="31">
+        <f ca="1" t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E29" s="43">
         <f ca="1" t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="2:5">
-      <c r="B8" s="41" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="2:5">
+      <c r="B30" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Conhecimento</v>
-      </c>
-      <c r="C8" s="29">
+        <v>Reflexos</v>
+      </c>
+      <c r="C30" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>15</v>
-      </c>
-      <c r="D8" s="29">
+        <v>17</v>
+      </c>
+      <c r="D30" s="33">
         <f ca="1" t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E8" s="42">
+        <v>5</v>
+      </c>
+      <c r="E30" s="46">
         <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" spans="2:5">
-      <c r="B9" s="38" t="str">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" ht="15" spans="2:5">
+      <c r="B31" s="47" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Cura</v>
-      </c>
-      <c r="C9" s="27">
+        <v>Religião</v>
+      </c>
+      <c r="C31" s="53">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>13</v>
-      </c>
-      <c r="D9" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E9" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" ht="15" spans="2:5">
-      <c r="B10" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Diplomacia</v>
-      </c>
-      <c r="C10" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>7</v>
-      </c>
-      <c r="D10" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E10" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="2:5">
-      <c r="B11" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Enganação</v>
-      </c>
-      <c r="C11" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>7</v>
-      </c>
-      <c r="D11" s="27">
+        <v>18</v>
+      </c>
+      <c r="D31" s="53">
         <f ca="1" t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="E11" s="39">
+      <c r="E31" s="48">
         <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="2:5">
-      <c r="B12" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Fortitude</v>
-      </c>
-      <c r="C12" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>6</v>
-      </c>
-      <c r="D12" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E12" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25" spans="2:5">
-      <c r="B13" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Furtividade</v>
-      </c>
-      <c r="C13" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>8</v>
-      </c>
-      <c r="D13" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="E13" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="2:5">
-      <c r="B14" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Guerra</v>
-      </c>
-      <c r="C14" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>17</v>
-      </c>
-      <c r="D14" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E14" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="2:5">
-      <c r="B15" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Iniciativa</v>
-      </c>
-      <c r="C15" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>8</v>
-      </c>
-      <c r="D15" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="E15" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="2:5">
-      <c r="B16" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Intimidação</v>
-      </c>
-      <c r="C16" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>7</v>
-      </c>
-      <c r="D16" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="E16" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="2:5">
-      <c r="B17" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Intuição</v>
-      </c>
-      <c r="C17" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>9</v>
-      </c>
-      <c r="D17" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="E17" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="2:5">
-      <c r="B18" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Investigação</v>
-      </c>
-      <c r="C18" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>15</v>
-      </c>
-      <c r="D18" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="E18" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="2:5">
-      <c r="B19" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Jogatina</v>
-      </c>
-      <c r="C19" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>7</v>
-      </c>
-      <c r="D19" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="E19" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="2:5">
-      <c r="B20" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ladinagem</v>
-      </c>
-      <c r="C20" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>8</v>
-      </c>
-      <c r="D20" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="E20" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="2:5">
-      <c r="B21" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Luta</v>
-      </c>
-      <c r="C21" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>12</v>
-      </c>
-      <c r="D21" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="E21" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="2:5">
-      <c r="B22" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Misticismo</v>
-      </c>
-      <c r="C22" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>17</v>
-      </c>
-      <c r="D22" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E22" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="2:5">
-      <c r="B23" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Nobreza</v>
-      </c>
-      <c r="C23" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>11</v>
-      </c>
-      <c r="D23" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E23" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="24" ht="30" spans="2:5">
-      <c r="B24" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ofício (Alquimista)</v>
-      </c>
-      <c r="C24" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>15</v>
-      </c>
-      <c r="D24" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E24" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="2:5">
-      <c r="B25" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ofício (Armeiro)</v>
-      </c>
-      <c r="C25" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>15</v>
-      </c>
-      <c r="D25" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E25" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" ht="30" spans="2:5">
-      <c r="B26" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Ofício (Engenhoqueiro)</v>
-      </c>
-      <c r="C26" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>15</v>
-      </c>
-      <c r="D26" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="E26" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="2:5">
-      <c r="B27" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Percepção</v>
-      </c>
-      <c r="C27" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>15</v>
-      </c>
-      <c r="D27" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="E27" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="2:5">
-      <c r="B28" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Pilotagem</v>
-      </c>
-      <c r="C28" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>8</v>
-      </c>
-      <c r="D28" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="E28" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="2:5">
-      <c r="B29" s="38" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Pontaria</v>
-      </c>
-      <c r="C29" s="27">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>8</v>
-      </c>
-      <c r="D29" s="27">
-        <f ca="1" t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="E29" s="39">
-        <f ca="1" t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="2:5">
-      <c r="B30" s="41" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Reflexos</v>
-      </c>
-      <c r="C30" s="29">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>12</v>
-      </c>
-      <c r="D30" s="29">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="E30" s="42">
-        <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" ht="15" spans="2:5">
-      <c r="B31" s="43" t="str">
-        <f>Tabela1[[#This Row],[Perícia]]</f>
-        <v>Religião</v>
-      </c>
-      <c r="C31" s="49">
-        <f>Tabela1[[#This Row],[Total]]</f>
-        <v>13</v>
-      </c>
-      <c r="D31" s="49">
-        <f ca="1" t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E31" s="44">
-        <f ca="1" t="shared" si="1"/>
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" ht="14.25"/>
@@ -5788,52 +5803,52 @@
   <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="23.2833333333333" customWidth="1"/>
-    <col min="3" max="3" width="15.425" customWidth="1"/>
-    <col min="4" max="4" width="11.8583333333333" customWidth="1"/>
-    <col min="5" max="5" width="10.5666666666667" customWidth="1"/>
+    <col min="2" max="2" width="23.25" customWidth="1"/>
+    <col min="3" max="3" width="15.375" customWidth="1"/>
+    <col min="4" max="4" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:8">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="E2" s="74" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="36"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="3" ht="14.25" spans="1:8">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="68" t="s">
+      <c r="B3" s="72" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="68" t="s">
+      <c r="C3" s="72" t="s">
         <v>89</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="31">
         <v>1</v>
       </c>
-      <c r="E3" s="37">
+      <c r="E3" s="41">
         <f t="shared" ref="E3:E35" si="0">IFERROR(VLOOKUP(D3,$G$3:$H$7,2,FALSE)^2*10,"")</f>
         <v>10</v>
       </c>
-      <c r="G3" s="38">
+      <c r="G3" s="42">
         <v>1</v>
       </c>
-      <c r="H3" s="39">
+      <c r="H3" s="43">
         <v>1</v>
       </c>
     </row>
@@ -5841,23 +5856,23 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="33">
         <v>1</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G4" s="41">
+      <c r="G4" s="45">
         <v>2</v>
       </c>
-      <c r="H4" s="42">
+      <c r="H4" s="46">
         <v>3</v>
       </c>
     </row>
@@ -5865,23 +5880,23 @@
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="72" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="31">
         <v>1</v>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G5" s="38">
+      <c r="G5" s="42">
         <v>3</v>
       </c>
-      <c r="H5" s="39">
+      <c r="H5" s="43">
         <v>6</v>
       </c>
     </row>
@@ -5889,23 +5904,23 @@
       <c r="A6">
         <v>2</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="33">
         <v>1</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="45">
         <v>4</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="46">
         <v>10</v>
       </c>
     </row>
@@ -5913,23 +5928,23 @@
       <c r="A7">
         <v>3</v>
       </c>
-      <c r="B7" s="68" t="s">
+      <c r="B7" s="72" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="31">
         <v>1</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E7" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="47">
         <v>5</v>
       </c>
-      <c r="H7" s="44">
+      <c r="H7" s="48">
         <v>15</v>
       </c>
     </row>
@@ -5937,16 +5952,16 @@
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="33">
         <v>1</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E8" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -5955,16 +5970,16 @@
       <c r="A9">
         <v>5</v>
       </c>
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="72" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="31">
         <v>1</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="41">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -5973,16 +5988,16 @@
       <c r="A10">
         <v>6</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="34" t="s">
         <v>97</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="33">
         <v>1</v>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -5991,16 +6006,16 @@
       <c r="A11">
         <v>7</v>
       </c>
-      <c r="B11" s="68" t="s">
+      <c r="B11" s="72" t="s">
         <v>98</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="31">
         <v>2</v>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="41">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
@@ -6009,16 +6024,16 @@
       <c r="A12">
         <v>8</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="33">
         <v>1</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -6027,16 +6042,16 @@
       <c r="A13">
         <v>9</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="72" t="s">
         <v>100</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="31">
         <v>2</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="41">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
@@ -6045,16 +6060,16 @@
       <c r="A14">
         <v>10</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="33">
         <v>2</v>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="44">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
@@ -6063,202 +6078,202 @@
       <c r="A15">
         <v>10</v>
       </c>
-      <c r="B15" s="68" t="s">
+      <c r="B15" s="72" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="31">
         <v>2</v>
       </c>
-      <c r="E15" s="37">
+      <c r="E15" s="41">
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
     </row>
     <row r="16" ht="15" spans="2:5">
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="33">
         <v>3</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="44">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="2:5">
-      <c r="B17" s="68"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="37" t="str">
+      <c r="B17" s="72"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" spans="2:5">
-      <c r="B18" s="30"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="40" t="str">
+      <c r="B18" s="34"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="19" ht="14.25" spans="2:5">
-      <c r="B19" s="68"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="37" t="str">
+      <c r="B19" s="72"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" spans="2:5">
-      <c r="B20" s="30"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="40" t="str">
+      <c r="B20" s="34"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:5">
-      <c r="B21" s="68"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="37" t="str">
+      <c r="B21" s="72"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" spans="2:5">
-      <c r="B22" s="30"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="40" t="str">
+      <c r="B22" s="34"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="23" ht="14.25" spans="2:5">
-      <c r="B23" s="68"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="37" t="str">
+      <c r="B23" s="72"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" spans="2:5">
-      <c r="B24" s="30"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="40" t="str">
+      <c r="B24" s="34"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="25" ht="14.25" spans="2:5">
-      <c r="B25" s="68"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="37" t="str">
+      <c r="B25" s="72"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" spans="2:5">
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="40" t="str">
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="27" ht="14.25" spans="2:5">
-      <c r="B27" s="68"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="37" t="str">
+      <c r="B27" s="72"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" spans="2:5">
-      <c r="B28" s="30"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="40" t="str">
+      <c r="B28" s="34"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="29" ht="14.25" spans="2:5">
-      <c r="B29" s="68"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="37" t="str">
+      <c r="B29" s="72"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" spans="2:5">
-      <c r="B30" s="30"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="40" t="str">
+      <c r="B30" s="34"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="31" ht="14.25" spans="2:5">
-      <c r="B31" s="68"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="37" t="str">
+      <c r="B31" s="72"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" spans="2:5">
-      <c r="B32" s="30"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="40" t="str">
+      <c r="B32" s="34"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="33" ht="14.25" spans="2:5">
-      <c r="B33" s="68"/>
-      <c r="C33" s="26"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="37" t="str">
+      <c r="B33" s="72"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="41" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" spans="2:5">
-      <c r="B34" s="30"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="40" t="str">
+      <c r="B34" s="34"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="35" ht="14.25" spans="2:5">
-      <c r="B35" s="69"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="47" t="str">
+      <c r="B35" s="73"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="51" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -6282,195 +6297,195 @@
   <dimension ref="B1:I26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="27.5666666666667" customWidth="1"/>
-    <col min="4" max="4" width="21.425" customWidth="1"/>
+    <col min="2" max="2" width="27.625" customWidth="1"/>
+    <col min="4" max="4" width="21.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25"/>
     <row r="2" ht="15.75" spans="2:6">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="36"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" ht="14.25" spans="2:6">
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="43" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:6">
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C4" s="33">
         <v>2</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="33">
         <v>0</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="44">
         <v>20</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="46">
         <v>7</v>
       </c>
     </row>
     <row r="5" ht="15" spans="2:6">
-      <c r="B5" s="43"/>
-      <c r="C5" s="49"/>
-      <c r="D5" s="49"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="44"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="48"/>
     </row>
     <row r="6" ht="15"/>
     <row r="7" ht="15.75" spans="2:8">
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="65"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="69"/>
     </row>
     <row r="8" ht="14.25" spans="2:8">
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="G8" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="39" t="s">
+      <c r="H8" s="43" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" ht="15" spans="2:8">
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40" t="s">
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44" t="s">
         <v>112</v>
       </c>
-      <c r="H9" s="42" t="s">
+      <c r="H9" s="46" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="10" ht="14.25" spans="2:8">
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="37">
+      <c r="E10" s="31"/>
+      <c r="F10" s="41">
         <v>6</v>
       </c>
-      <c r="G10" s="37" t="s">
+      <c r="G10" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="H10" s="39" t="s">
+      <c r="H10" s="43" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="11" ht="15" spans="2:8">
-      <c r="B11" s="41"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="42"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="44"/>
+      <c r="G11" s="44"/>
+      <c r="H11" s="46"/>
     </row>
     <row r="12" ht="14.25" spans="2:8">
-      <c r="B12" s="38"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="39"/>
+      <c r="B12" s="42"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="43"/>
     </row>
     <row r="13" ht="15.75" spans="2:8">
-      <c r="B13" s="45"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="46"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="50"/>
     </row>
     <row r="14" ht="15"/>
     <row r="15" ht="15.75" spans="2:9">
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="39" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="36"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="40"/>
     </row>
     <row r="16" ht="14.25" spans="2:9">
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="58" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54" t="s">
+      <c r="D16" s="58"/>
+      <c r="E16" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="F16" s="54" t="s">
+      <c r="F16" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="54" t="s">
+      <c r="G16" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="H16" s="54" t="s">
+      <c r="H16" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="I16" s="67" t="s">
+      <c r="I16" s="71" t="s">
         <v>106</v>
       </c>
     </row>
@@ -6478,92 +6493,92 @@
       <c r="B17" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="98" t="s">
         <v>122</v>
       </c>
       <c r="D17" s="11"/>
-      <c r="E17" s="29">
+      <c r="E17" s="33">
         <v>1</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="33">
         <v>0.1</v>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="33">
         <f>PRODUCT(E17:F17)</f>
         <v>0.1</v>
       </c>
-      <c r="H17" s="29"/>
-      <c r="I17" s="42">
+      <c r="H17" s="33"/>
+      <c r="I17" s="46">
         <f>PRODUCT(H17,E17)</f>
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="14.25" spans="2:9">
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="27">
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="31">
         <v>3</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="31">
         <v>0.1</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="31">
         <f t="shared" ref="G18:G21" si="0">PRODUCT(E18:F18)</f>
         <v>0.3</v>
       </c>
-      <c r="H18" s="27"/>
-      <c r="I18" s="39">
+      <c r="H18" s="31"/>
+      <c r="I18" s="43">
         <f t="shared" ref="I18:I21" si="1">PRODUCT(H18,E18)</f>
         <v>3</v>
       </c>
     </row>
     <row r="19" ht="15" spans="2:9">
-      <c r="B19" s="41"/>
+      <c r="B19" s="45"/>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29">
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H19" s="29"/>
-      <c r="I19" s="42">
+      <c r="H19" s="33"/>
+      <c r="I19" s="46">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" ht="14.25" spans="2:9">
-      <c r="B20" s="38"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27">
+      <c r="B20" s="42"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" s="27"/>
-      <c r="I20" s="39">
+      <c r="H20" s="31"/>
+      <c r="I20" s="43">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" ht="15.75" spans="2:9">
-      <c r="B21" s="45"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52">
+      <c r="B21" s="49"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="56"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H21" s="52"/>
-      <c r="I21" s="46">
+      <c r="H21" s="56"/>
+      <c r="I21" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -6573,7 +6588,7 @@
       <c r="B23" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="57">
+      <c r="C23" s="61">
         <f>SUM(G17:G21,F9:F13,F4:F5)</f>
         <v>13.4</v>
       </c>
@@ -6583,24 +6598,24 @@
       </c>
     </row>
     <row r="24" ht="14.25" spans="2:4">
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="62" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="59">
+      <c r="C24" s="63">
         <f>Ligma!C3*10</f>
         <v>160</v>
       </c>
-      <c r="D24" s="60"/>
+      <c r="D24" s="64"/>
     </row>
     <row r="25" ht="15.75" spans="2:4">
       <c r="B25" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="61" t="str">
+      <c r="C25" s="65" t="str">
         <f>IF(C23&gt;D23,"Sobrecarga","Sem Penalidade")</f>
         <v>Sem Penalidade</v>
       </c>
-      <c r="D25" s="62"/>
+      <c r="D25" s="66"/>
     </row>
     <row r="26" ht="14.25"/>
   </sheetData>
@@ -6630,1246 +6645,1246 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="9.56666666666667" customWidth="1"/>
-    <col min="4" max="4" width="10.5666666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.2833333333333" customWidth="1"/>
-    <col min="6" max="7" width="11.425" customWidth="1"/>
-    <col min="8" max="8" width="11.1416666666667" customWidth="1"/>
-    <col min="9" max="9" width="21.425" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
-    <col min="11" max="11" width="13.8583333333333" customWidth="1"/>
-    <col min="12" max="12" width="21.425" customWidth="1"/>
-    <col min="13" max="13" width="26.7083333333333" customWidth="1"/>
-    <col min="14" max="14" width="9.85833333333333" customWidth="1"/>
-    <col min="15" max="15" width="12.5666666666667" customWidth="1"/>
+    <col min="3" max="3" width="9.625" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="13.25" customWidth="1"/>
+    <col min="6" max="7" width="11.375" customWidth="1"/>
+    <col min="8" max="8" width="11.125" customWidth="1"/>
+    <col min="9" max="9" width="21.375" customWidth="1"/>
+    <col min="10" max="10" width="10.125" customWidth="1"/>
+    <col min="11" max="11" width="13.875" customWidth="1"/>
+    <col min="12" max="12" width="21.375" customWidth="1"/>
+    <col min="13" max="13" width="26.75" customWidth="1"/>
+    <col min="14" max="14" width="9.875" customWidth="1"/>
+    <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="O2" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="P2" s="36"/>
+      <c r="P2" s="40"/>
     </row>
     <row r="3" ht="14.25" spans="2:16">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="31">
         <f>VLOOKUP(C3,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E3" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E3" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F3" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="F3" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27">
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
         <v>8</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="O3" s="38" t="s">
+      <c r="O3" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="39">
+      <c r="P3" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:16">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="33">
         <f>VLOOKUP(C4,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E4" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E4" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F4" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="F4" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29">
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
         <v>7</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="M4" s="40" t="s">
+      <c r="M4" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="O4" s="41" t="s">
+      <c r="O4" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="P4" s="42">
+      <c r="P4" s="46">
         <v>4</v>
       </c>
     </row>
     <row r="5" ht="15" spans="2:16">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="31">
         <f>VLOOKUP(C5,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E5" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F5" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="F5" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27">
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
         <v>8</v>
       </c>
-      <c r="K5" s="27" t="s">
+      <c r="K5" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L5" s="27" t="s">
+      <c r="L5" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="M5" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="O5" s="43" t="s">
+      <c r="O5" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="48">
         <v>6</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="2:13">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="33">
         <f>VLOOKUP(C6,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E6" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E6" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F6" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="F6" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29">
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
         <v>7</v>
       </c>
-      <c r="K6" s="29" t="s">
+      <c r="K6" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="L6" s="29" t="s">
+      <c r="L6" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="44" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="31">
         <f>VLOOKUP(C7,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E7" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E7" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F7" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="F7" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27">
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
         <v>8</v>
       </c>
-      <c r="K7" s="27" t="s">
+      <c r="K7" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="O7" s="35" t="s">
+      <c r="O7" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="P7" s="36"/>
+      <c r="P7" s="40"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="2:16">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="33">
         <f>VLOOKUP(C8,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E8" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E8" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F8" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="F8" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>20</v>
+      </c>
+      <c r="K8" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L8" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M8" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="O8" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>15</v>
-      </c>
-      <c r="K8" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="L8" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="M8" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="O8" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="39">
+      <c r="P8" s="43">
         <f>VLOOKUP(O8,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="15" spans="2:16">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="31">
         <f>VLOOKUP(C9,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E9" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E9" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F9" s="27">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>4</v>
-      </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27">
+      <c r="F9" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>13</v>
-      </c>
-      <c r="K9" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L9" s="27" t="s">
+      <c r="L9" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="O9" s="41" t="s">
+      <c r="O9" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="P9" s="42">
+      <c r="P9" s="46">
         <f>VLOOKUP(O9,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" ht="15" spans="2:16">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="33">
         <f>VLOOKUP(C10,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E10" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E10" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F10" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="F10" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29">
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
         <v>7</v>
       </c>
-      <c r="K10" s="29" t="s">
+      <c r="K10" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="L10" s="29" t="s">
+      <c r="L10" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="M10" s="40" t="s">
+      <c r="M10" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="O10" s="38" t="s">
+      <c r="O10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="39">
+      <c r="P10" s="43">
         <f>VLOOKUP(O10,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>-2</v>
       </c>
     </row>
     <row r="11" ht="15" spans="2:16">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="31">
         <f>VLOOKUP(C11,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E11" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E11" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F11" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="F11" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27">
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
         <v>7</v>
       </c>
-      <c r="K11" s="27" t="s">
+      <c r="K11" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L11" s="27" t="s">
+      <c r="L11" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M11" s="37" t="s">
+      <c r="M11" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="O11" s="41" t="s">
+      <c r="O11" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="42">
+      <c r="P11" s="46">
         <f>VLOOKUP(O11,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>6</v>
       </c>
     </row>
     <row r="12" ht="15" spans="2:16">
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="33">
         <f>VLOOKUP(C12,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E12" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E12" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F12" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="F12" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29">
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
         <v>6</v>
       </c>
-      <c r="K12" s="29" t="s">
+      <c r="K12" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="L12" s="29" t="s">
+      <c r="L12" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="M12" s="40" t="s">
+      <c r="M12" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="O12" s="38" t="s">
+      <c r="O12" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="P12" s="39">
+      <c r="P12" s="43">
         <f>VLOOKUP(O12,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="2:16">
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="31">
         <f>VLOOKUP(C13,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E13" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E13" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F13" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="F13" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27">
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
         <v>8</v>
       </c>
-      <c r="K13" s="27" t="s">
+      <c r="K13" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L13" s="27" t="s">
+      <c r="L13" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="37" t="s">
+      <c r="M13" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="O13" s="45" t="s">
+      <c r="O13" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="P13" s="46">
+      <c r="P13" s="50">
         <f>VLOOKUP(O13,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="2:13">
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="33">
         <f>VLOOKUP(C14,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E14" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E14" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F14" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="F14" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33">
+        <v>2</v>
+      </c>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>22</v>
+      </c>
+      <c r="K14" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M14" s="44" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" ht="14.25" spans="2:13">
+      <c r="B15" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="D15" s="31">
+        <f>VLOOKUP(C15,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E15" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F15" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>8</v>
+      </c>
+      <c r="K15" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="L15" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="M15" s="41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="2:13">
+      <c r="B16" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="33">
+        <f>VLOOKUP(C16,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="E16" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F16" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>7</v>
+      </c>
+      <c r="K16" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="L16" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="M16" s="44" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" ht="14.25" spans="2:13">
+      <c r="B17" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D17" s="31">
+        <f>VLOOKUP(C17,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29">
+      <c r="E17" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F17" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>9</v>
+      </c>
+      <c r="K17" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="L17" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="M17" s="41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="2:13">
+      <c r="B18" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D18" s="33">
+        <f>VLOOKUP(C18,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E18" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F18" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>20</v>
+      </c>
+      <c r="K18" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L18" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="M18" s="44" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" ht="14.25" spans="2:13">
+      <c r="B19" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="31">
+        <f>VLOOKUP(C19,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29">
+      <c r="E19" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F19" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>7</v>
+      </c>
+      <c r="K19" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="L19" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="M19" s="41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="2:13">
+      <c r="B20" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="33">
+        <f>VLOOKUP(C20,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E20" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F20" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>8</v>
+      </c>
+      <c r="K20" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="L20" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M20" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" spans="2:13">
+      <c r="B21" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" s="31">
+        <f>VLOOKUP(C21,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E21" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F21" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
         <v>17</v>
       </c>
-      <c r="K14" s="29" t="s">
+      <c r="K21" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L14" s="29" t="s">
+      <c r="L21" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="M21" s="41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" ht="15" spans="2:13">
+      <c r="B22" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="33">
+        <f>VLOOKUP(C22,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E22" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F22" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G22" s="33">
+        <v>2</v>
+      </c>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>22</v>
+      </c>
+      <c r="K22" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="M14" s="40" t="s">
+      <c r="L22" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M22" s="44" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="2:13">
-      <c r="B15" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="C15" s="27" t="s">
+    <row r="23" ht="14.25" spans="2:13">
+      <c r="B23" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="D23" s="31">
+        <f>VLOOKUP(C23,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E23" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F23" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>11</v>
+      </c>
+      <c r="K23" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="L23" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="M23" s="41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" ht="15" spans="2:13">
+      <c r="B24" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D24" s="33">
+        <f>VLOOKUP(C24,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E24" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F24" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>20</v>
+      </c>
+      <c r="K24" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L24" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M24" s="44" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" spans="2:13">
+      <c r="B25" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" s="31">
+        <f>VLOOKUP(C25,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E25" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F25" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>20</v>
+      </c>
+      <c r="K25" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L25" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="M25" s="41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" ht="15" spans="2:13">
+      <c r="B26" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" s="33">
+        <f>VLOOKUP(C26,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="E26" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F26" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>20</v>
+      </c>
+      <c r="K26" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L26" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M26" s="44" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" ht="14.25" spans="2:13">
+      <c r="B27" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" s="31">
+        <f>VLOOKUP(C27,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E27" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F27" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G27" s="31">
+        <v>2</v>
+      </c>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>20</v>
+      </c>
+      <c r="K27" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L27" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="M27" s="41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="2:13">
+      <c r="B28" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="D15" s="27">
-        <f>VLOOKUP(C15,Ligma!$B$3:$D$8,3,FALSE)</f>
+      <c r="D28" s="33">
+        <f>VLOOKUP(C28,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E15" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E28" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F15" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="F28" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27">
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
         <v>8</v>
       </c>
-      <c r="K15" s="27" t="s">
+      <c r="K28" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="L15" s="27" t="s">
+      <c r="L28" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="M28" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="M15" s="37" t="s">
+    </row>
+    <row r="29" ht="14.25" spans="2:13">
+      <c r="B29" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" s="31">
+        <f>VLOOKUP(C29,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E29" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F29" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>8</v>
+      </c>
+      <c r="K29" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="L29" s="31" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="16" ht="15" spans="2:13">
-      <c r="B16" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="C16" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="D16" s="29">
-        <f>VLOOKUP(C16,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E16" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="M29" s="41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" ht="15" spans="2:13">
+      <c r="B30" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="D30" s="33">
+        <f>VLOOKUP(C30,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="E30" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F16" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+      <c r="F30" s="33">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>17</v>
+      </c>
+      <c r="K30" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="L30" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="M30" s="44" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" ht="14.25" spans="2:13">
+      <c r="B31" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="D31" s="31">
+        <f>VLOOKUP(C31,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E31" s="31">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F31" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31">
+        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
+        <v>18</v>
+      </c>
+      <c r="K31" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L31" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="M31" s="41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="2:13">
+      <c r="B32" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D32" s="33">
+        <f>VLOOKUP(C32,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E32" s="33">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
+        <v>5</v>
+      </c>
+      <c r="F32" s="33" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K16" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="L16" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M16" s="40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="2:13">
-      <c r="B17" s="26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="D17" s="27">
-        <f>VLOOKUP(C17,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E17" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F17" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27">
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
         <v>9</v>
       </c>
-      <c r="K17" s="27" t="s">
+      <c r="K32" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="L17" s="27" t="s">
+      <c r="L32" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="M17" s="37" t="s">
+      <c r="M32" s="44" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:13">
-      <c r="B18" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="D18" s="29">
-        <f>VLOOKUP(C18,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E18" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F18" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>4</v>
-      </c>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>15</v>
-      </c>
-      <c r="K18" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="L18" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M18" s="40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="2:13">
-      <c r="B19" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19" s="27">
-        <f>VLOOKUP(C19,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>2</v>
-      </c>
-      <c r="E19" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F19" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K19" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="L19" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="20" ht="15" spans="2:13">
-      <c r="B20" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="D20" s="29">
-        <f>VLOOKUP(C20,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E20" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F20" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K20" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="L20" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="M20" s="40" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="2:13">
-      <c r="B21" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="D21" s="27">
-        <f>VLOOKUP(C21,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E21" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F21" s="27">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>4</v>
-      </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>12</v>
-      </c>
-      <c r="K21" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="L21" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="M21" s="37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="2:13">
-      <c r="B22" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="D22" s="29">
-        <f>VLOOKUP(C22,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E22" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F22" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>4</v>
-      </c>
-      <c r="G22" s="29">
-        <v>2</v>
-      </c>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>17</v>
-      </c>
-      <c r="K22" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="L22" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="M22" s="40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="2:13">
-      <c r="B23" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="D23" s="27">
-        <f>VLOOKUP(C23,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E23" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F23" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K23" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="L23" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="24" ht="15" spans="2:13">
-      <c r="B24" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="C24" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="D24" s="29">
-        <f>VLOOKUP(C24,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E24" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F24" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>4</v>
-      </c>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>15</v>
-      </c>
-      <c r="K24" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="M24" s="40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="2:13">
-      <c r="B25" s="26" t="s">
-        <v>167</v>
-      </c>
-      <c r="C25" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="D25" s="27">
-        <f>VLOOKUP(C25,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E25" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F25" s="27">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>4</v>
-      </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>15</v>
-      </c>
-      <c r="K25" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="L25" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="M25" s="37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="26" ht="15" spans="2:13">
-      <c r="B26" s="30" t="s">
-        <v>168</v>
-      </c>
-      <c r="C26" s="29" t="s">
-        <v>149</v>
-      </c>
-      <c r="D26" s="29">
-        <f>VLOOKUP(C26,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
-      </c>
-      <c r="E26" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F26" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>4</v>
-      </c>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>15</v>
-      </c>
-      <c r="K26" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="L26" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="M26" s="40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="2:13">
-      <c r="B27" s="26" t="s">
-        <v>169</v>
-      </c>
-      <c r="C27" s="27" t="s">
+    <row r="33" ht="14.25" spans="2:13">
+      <c r="B33" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="D27" s="27">
-        <f>VLOOKUP(C27,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E27" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F27" s="27">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>4</v>
-      </c>
-      <c r="G27" s="27">
-        <v>2</v>
-      </c>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>15</v>
-      </c>
-      <c r="K27" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="L27" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="M27" s="37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="2:13">
-      <c r="B28" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="D28" s="29">
-        <f>VLOOKUP(C28,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E28" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F28" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K28" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="L28" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="M28" s="40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="2:13">
-      <c r="B29" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C29" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D29" s="27">
-        <f>VLOOKUP(C29,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E29" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F29" s="27" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K29" s="27" t="s">
-        <v>138</v>
-      </c>
-      <c r="L29" s="27" t="s">
-        <v>139</v>
-      </c>
-      <c r="M29" s="37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="2:13">
-      <c r="B30" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="C30" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="D30" s="29">
-        <f>VLOOKUP(C30,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>3</v>
-      </c>
-      <c r="E30" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F30" s="29">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>4</v>
-      </c>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>12</v>
-      </c>
-      <c r="K30" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="L30" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M30" s="40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" ht="14.25" spans="2:13">
-      <c r="B31" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="C31" s="27" t="s">
-        <v>151</v>
-      </c>
-      <c r="D31" s="27">
-        <f>VLOOKUP(C31,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E31" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F31" s="27">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>4</v>
-      </c>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>13</v>
-      </c>
-      <c r="K31" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="L31" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="M31" s="37" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="32" ht="15" spans="2:13">
-      <c r="B32" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="C32" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="D32" s="29">
-        <f>VLOOKUP(C32,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E32" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F32" s="29" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29">
-        <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>9</v>
-      </c>
-      <c r="K32" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="L32" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M32" s="40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="2:13">
-      <c r="B33" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="D33" s="32">
+      <c r="D33" s="36">
         <f>VLOOKUP(C33,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E33" s="32">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
+      <c r="E33" s="36">
+        <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F33" s="32">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v>4</v>
-      </c>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32">
+      <c r="F33" s="36">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <v>9</v>
+      </c>
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>13</v>
-      </c>
-      <c r="K33" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="K33" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="L33" s="32" t="s">
+      <c r="L33" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="M33" s="47" t="s">
+      <c r="M33" s="51" t="s">
         <v>139</v>
       </c>
     </row>
@@ -7894,1246 +7909,1246 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="9.56666666666667" customWidth="1"/>
-    <col min="4" max="4" width="10.5666666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.2833333333333" customWidth="1"/>
-    <col min="6" max="7" width="11.425" customWidth="1"/>
-    <col min="8" max="8" width="11.1416666666667" customWidth="1"/>
-    <col min="9" max="9" width="21.425" customWidth="1"/>
-    <col min="10" max="10" width="10.1416666666667" customWidth="1"/>
-    <col min="11" max="11" width="13.8583333333333" customWidth="1"/>
-    <col min="12" max="12" width="21.425" customWidth="1"/>
-    <col min="13" max="13" width="26.7083333333333" customWidth="1"/>
-    <col min="14" max="14" width="9.85833333333333" customWidth="1"/>
-    <col min="15" max="15" width="12.5666666666667" customWidth="1"/>
+    <col min="3" max="3" width="9.625" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="5" max="5" width="13.25" customWidth="1"/>
+    <col min="6" max="7" width="11.375" customWidth="1"/>
+    <col min="8" max="8" width="11.125" customWidth="1"/>
+    <col min="9" max="9" width="21.375" customWidth="1"/>
+    <col min="10" max="10" width="10.125" customWidth="1"/>
+    <col min="11" max="11" width="13.875" customWidth="1"/>
+    <col min="12" max="12" width="21.375" customWidth="1"/>
+    <col min="13" max="13" width="26.75" customWidth="1"/>
+    <col min="14" max="14" width="9.875" customWidth="1"/>
+    <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25"/>
     <row r="2" ht="15" customHeight="1" spans="2:16">
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="25" t="s">
+      <c r="E2" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="G2" s="25" t="s">
+      <c r="G2" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="25" t="s">
+      <c r="H2" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="J2" s="25" t="s">
+      <c r="J2" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>132</v>
       </c>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="37" t="s">
         <v>133</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="O2" s="39" t="s">
         <v>135</v>
       </c>
-      <c r="P2" s="36"/>
+      <c r="P2" s="40"/>
     </row>
     <row r="3" ht="14.25" spans="2:16">
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="31">
         <f>VLOOKUP(C3,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E3" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F3" s="27" t="str">
+      <c r="E3" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F3" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27">
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!D16,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K3" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="O3" s="38" t="s">
+      <c r="O3" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="39">
+      <c r="P3" s="43">
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="15" spans="2:16">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="33">
         <f>VLOOKUP(C4,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E4" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F4" s="29" t="str">
+      <c r="E4" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F4" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29">
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!D17,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K4" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="M4" s="40" t="s">
+      <c r="M4" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="O4" s="41" t="s">
+      <c r="O4" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="P4" s="42">
+      <c r="P4" s="46">
         <v>4</v>
       </c>
     </row>
     <row r="5" ht="15" spans="2:16">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="31">
         <f>VLOOKUP(C5,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E5" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F5" s="27" t="str">
+      <c r="E5" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F5" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27">
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C1,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K5" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L5" s="27" t="s">
+      <c r="L5" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M5" s="37" t="s">
+      <c r="M5" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="O5" s="43" t="s">
+      <c r="O5" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="48">
         <v>6</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="2:13">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="33">
         <f>VLOOKUP(C6,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E6" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F6" s="29" t="str">
+      <c r="E6" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F6" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29">
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C2,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K6" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="L6" s="29" t="s">
+      <c r="L6" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="44" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="2:16">
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="31">
         <f>VLOOKUP(C7,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E7" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F7" s="27" t="str">
+      <c r="E7" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F7" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27">
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C3,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K7" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M7" s="37" t="s">
+      <c r="M7" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="O7" s="35" t="s">
+      <c r="O7" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="P7" s="36"/>
+      <c r="P7" s="40"/>
     </row>
     <row r="8" ht="15" customHeight="1" spans="2:16">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="33">
         <f>VLOOKUP(C8,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E8" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F8" s="29">
+      <c r="E8" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F8" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>4</v>
       </c>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29">
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C4,0)</f>
-        <v>15</v>
-      </c>
-      <c r="K8" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="K8" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="L8" s="29" t="s">
+      <c r="L8" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="M8" s="40" t="s">
+      <c r="M8" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="O8" s="38" t="s">
+      <c r="O8" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="P8" s="39">
+      <c r="P8" s="43">
         <f>VLOOKUP(O8,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="15" spans="2:16">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="31">
         <f>VLOOKUP(C9,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E9" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F9" s="27">
+      <c r="E9" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F9" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>4</v>
       </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27">
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C5,0)</f>
-        <v>13</v>
-      </c>
-      <c r="K9" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L9" s="27" t="s">
+      <c r="L9" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="O9" s="41" t="s">
+      <c r="O9" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="P9" s="42">
+      <c r="P9" s="46">
         <f>VLOOKUP(O9,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
     </row>
     <row r="10" ht="15" spans="2:16">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="33">
         <f>VLOOKUP(C10,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E10" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F10" s="29" t="str">
+      <c r="E10" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F10" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29">
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C6,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K10" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="L10" s="29" t="s">
+      <c r="L10" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="M10" s="40" t="s">
+      <c r="M10" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="O10" s="38" t="s">
+      <c r="O10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="39">
+      <c r="P10" s="43">
         <f>VLOOKUP(O10,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>-2</v>
       </c>
     </row>
     <row r="11" ht="15" spans="2:16">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="31">
         <f>VLOOKUP(C11,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E11" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F11" s="27" t="str">
+      <c r="E11" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F11" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27">
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C7,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K11" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L11" s="27" t="s">
+      <c r="L11" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M11" s="37" t="s">
+      <c r="M11" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="O11" s="41" t="s">
+      <c r="O11" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="P11" s="42">
+      <c r="P11" s="46">
         <f>VLOOKUP(O11,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>6</v>
       </c>
     </row>
     <row r="12" ht="15" spans="2:16">
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="33">
         <f>VLOOKUP(C12,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="E12" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F12" s="29" t="str">
+      <c r="E12" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F12" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29">
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C8,0)</f>
-        <v>6</v>
-      </c>
-      <c r="K12" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="L12" s="29" t="s">
+      <c r="L12" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="M12" s="40" t="s">
+      <c r="M12" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="O12" s="38" t="s">
+      <c r="O12" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="P12" s="39">
+      <c r="P12" s="43">
         <f>VLOOKUP(O12,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>2</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="2:16">
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="31">
         <f>VLOOKUP(C13,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E13" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F13" s="27" t="str">
+      <c r="E13" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F13" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27">
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C9,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K13" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="K13" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L13" s="27" t="s">
+      <c r="L13" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M13" s="37" t="s">
+      <c r="M13" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="O13" s="45" t="s">
+      <c r="O13" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="P13" s="46">
+      <c r="P13" s="50">
         <f>VLOOKUP(O13,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="2:13">
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="33">
         <f>VLOOKUP(C14,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E14" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F14" s="29">
+      <c r="E14" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F14" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>4</v>
       </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29">
+      <c r="G14" s="33"/>
+      <c r="H14" s="33">
         <v>1</v>
       </c>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29">
+      <c r="I14" s="33"/>
+      <c r="J14" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C10,0)</f>
-        <v>16</v>
-      </c>
-      <c r="K14" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="L14" s="29" t="s">
+      <c r="L14" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="M14" s="40" t="s">
+      <c r="M14" s="44" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="15" ht="14.25" spans="2:13">
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="31">
         <f>VLOOKUP(C15,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E15" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F15" s="27" t="str">
+      <c r="E15" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F15" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27">
+      <c r="G15" s="31"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C11,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K15" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L15" s="27" t="s">
+      <c r="L15" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M15" s="37" t="s">
+      <c r="M15" s="41" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="16" ht="15" spans="2:13">
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="33">
         <f>VLOOKUP(C16,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E16" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F16" s="29" t="str">
+      <c r="E16" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F16" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29">
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C12,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K16" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="K16" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="L16" s="29" t="s">
+      <c r="L16" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="M16" s="40" t="s">
+      <c r="M16" s="44" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="17" ht="14.25" spans="2:13">
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="31">
         <f>VLOOKUP(C17,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E17" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F17" s="27" t="str">
+      <c r="E17" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F17" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27">
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C13,0)</f>
-        <v>9</v>
-      </c>
-      <c r="K17" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="K17" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L17" s="27" t="s">
+      <c r="L17" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M17" s="37" t="s">
+      <c r="M17" s="41" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="18" ht="15" spans="2:13">
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="33">
         <f>VLOOKUP(C18,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E18" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F18" s="29">
+      <c r="E18" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F18" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>4</v>
       </c>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29">
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C14,0)</f>
-        <v>15</v>
-      </c>
-      <c r="K18" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="K18" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="L18" s="29" t="s">
+      <c r="L18" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="M18" s="40" t="s">
+      <c r="M18" s="44" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="19" ht="14.25" spans="2:13">
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="31">
         <f>VLOOKUP(C19,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>2</v>
       </c>
-      <c r="E19" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F19" s="27" t="str">
+      <c r="E19" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F19" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27">
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C15,0)</f>
-        <v>7</v>
-      </c>
-      <c r="K19" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="K19" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L19" s="27" t="s">
+      <c r="L19" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="M19" s="37" t="s">
+      <c r="M19" s="41" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="20" ht="15" spans="2:13">
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="33">
         <f>VLOOKUP(C20,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E20" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F20" s="29" t="str">
+      <c r="E20" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F20" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29">
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C16,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K20" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="K20" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="L20" s="29" t="s">
+      <c r="L20" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="M20" s="40" t="s">
+      <c r="M20" s="44" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="21" ht="14.25" spans="2:13">
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="31">
         <f>VLOOKUP(C21,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E21" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F21" s="27">
+      <c r="E21" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F21" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>4</v>
       </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27">
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C17,0)</f>
-        <v>12</v>
-      </c>
-      <c r="K21" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L21" s="27" t="s">
+      <c r="L21" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M21" s="37" t="s">
+      <c r="M21" s="41" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="22" ht="15" spans="2:13">
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="32" t="s">
         <v>164</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="33">
         <f>VLOOKUP(C22,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E22" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F22" s="29">
+      <c r="E22" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F22" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>4</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="33">
         <v>2</v>
       </c>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29">
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C18,0)</f>
-        <v>17</v>
-      </c>
-      <c r="K22" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="K22" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="L22" s="29" t="s">
+      <c r="L22" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="M22" s="40" t="s">
+      <c r="M22" s="44" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="23" ht="14.25" spans="2:13">
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="D23" s="27">
+      <c r="D23" s="31">
         <f>VLOOKUP(C23,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E23" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F23" s="27" t="str">
+      <c r="E23" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F23" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27">
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C19,0)</f>
-        <v>11</v>
-      </c>
-      <c r="K23" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L23" s="27" t="s">
+      <c r="L23" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="M23" s="37" t="s">
+      <c r="M23" s="41" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="24" ht="15" spans="2:13">
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="33">
         <f>VLOOKUP(C24,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E24" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F24" s="29">
+      <c r="E24" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F24" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>4</v>
       </c>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29">
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C20,0)</f>
-        <v>15</v>
-      </c>
-      <c r="K24" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="K24" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="L24" s="29" t="s">
+      <c r="L24" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="M24" s="40" t="s">
+      <c r="M24" s="44" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="25" ht="14.25" spans="2:13">
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="31">
         <f>VLOOKUP(C25,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E25" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F25" s="27">
+      <c r="E25" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F25" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>4</v>
       </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27">
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C21,0)</f>
-        <v>15</v>
-      </c>
-      <c r="K25" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L25" s="27" t="s">
+      <c r="L25" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="M25" s="37" t="s">
+      <c r="M25" s="41" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="26" ht="15" spans="2:13">
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="33">
         <f>VLOOKUP(C26,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>6</v>
       </c>
-      <c r="E26" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F26" s="29">
+      <c r="E26" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F26" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>4</v>
       </c>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29">
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C22,0)</f>
-        <v>15</v>
-      </c>
-      <c r="K26" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="L26" s="29" t="s">
+      <c r="L26" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="M26" s="40" t="s">
+      <c r="M26" s="44" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="27" ht="14.25" spans="2:13">
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="31">
         <f>VLOOKUP(C27,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E27" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F27" s="27">
+      <c r="E27" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F27" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>4</v>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="31">
         <v>2</v>
       </c>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27">
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!D40,0)</f>
-        <v>15</v>
-      </c>
-      <c r="K27" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="L27" s="27" t="s">
+      <c r="L27" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M27" s="37" t="s">
+      <c r="M27" s="41" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="28" ht="15" spans="2:13">
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="33">
         <f>VLOOKUP(C28,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E28" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F28" s="29" t="str">
+      <c r="E28" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F28" s="33" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29">
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!K1,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K28" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="K28" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="L28" s="29" t="s">
+      <c r="L28" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="M28" s="40" t="s">
+      <c r="M28" s="44" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="29" ht="14.25" spans="2:13">
-      <c r="B29" s="26" t="s">
+      <c r="B29" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="31">
         <f>VLOOKUP(C29,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E29" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F29" s="27" t="str">
+      <c r="E29" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F29" s="31" t="str">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27">
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!K2,0)</f>
-        <v>8</v>
-      </c>
-      <c r="K29" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="K29" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="L29" s="27" t="s">
+      <c r="L29" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="M29" s="37" t="s">
+      <c r="M29" s="41" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="30" ht="15" spans="2:13">
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="33">
         <f>VLOOKUP(C30,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>3</v>
       </c>
-      <c r="E30" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F30" s="29">
+      <c r="E30" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F30" s="33">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>4</v>
       </c>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29">
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
-        <v>12</v>
-      </c>
-      <c r="K30" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="L30" s="29" t="s">
+      <c r="L30" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="M30" s="40" t="s">
+      <c r="M30" s="44" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="31" ht="14.25" spans="2:13">
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="31">
         <f>VLOOKUP(C31,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E31" s="27">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F31" s="27">
+      <c r="E31" s="31">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F31" s="31">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>4</v>
       </c>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27">
+      <c r="G31" s="31"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31">
+        <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
+        <v>17</v>
+      </c>
+      <c r="K31" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="L31" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="M31" s="41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" ht="15" spans="2:13">
+      <c r="B32" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="D32" s="33">
+        <f>VLOOKUP(C32,Ligma!$B$3:$D$8,3,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="E32" s="33">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F32" s="33" t="str">
+        <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
         <v>13</v>
       </c>
-      <c r="K31" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="L31" s="27" t="s">
-        <v>140</v>
-      </c>
-      <c r="M31" s="37" t="s">
+      <c r="K32" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="L32" s="33" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="32" ht="15" spans="2:13">
-      <c r="B32" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="C32" s="29" t="s">
+      <c r="M32" s="44" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" ht="14.25" spans="2:13">
+      <c r="B33" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="C33" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="D32" s="29">
-        <f>VLOOKUP(C32,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>4</v>
-      </c>
-      <c r="E32" s="29">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F32" s="29" t="str">
-        <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29">
-        <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
-        <v>9</v>
-      </c>
-      <c r="K32" s="29" t="s">
-        <v>138</v>
-      </c>
-      <c r="L32" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="M32" s="40" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="33" ht="14.25" spans="2:13">
-      <c r="B33" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="D33" s="32">
+      <c r="D33" s="36">
         <f>VLOOKUP(C33,Ligma!$B$3:$D$8,3,FALSE)</f>
         <v>4</v>
       </c>
-      <c r="E33" s="32">
-        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$J$22,2,FALSE)</f>
-        <v>5</v>
-      </c>
-      <c r="F33" s="32">
+      <c r="E33" s="36">
+        <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="F33" s="36">
         <f>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v>4</v>
       </c>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32">
+      <c r="G33" s="36"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="36">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</f>
-        <v>13</v>
-      </c>
-      <c r="K33" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="L33" s="32" t="s">
+      <c r="L33" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="M33" s="47" t="s">
+      <c r="M33" s="51" t="s">
         <v>139</v>
       </c>
     </row>
@@ -9154,18 +9169,18 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:M23"/>
+  <dimension ref="B1:N23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="3" width="10.2833333333333" customWidth="1"/>
-    <col min="4" max="4" width="12.2833333333333" customWidth="1"/>
-    <col min="8" max="8" width="20.2833333333333" customWidth="1"/>
-    <col min="9" max="9" width="19.8583333333333" customWidth="1"/>
-    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="2" max="3" width="10.25" customWidth="1"/>
+    <col min="4" max="4" width="12.25" customWidth="1"/>
+    <col min="8" max="8" width="20.25" customWidth="1"/>
+    <col min="9" max="10" width="19.875" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:13">
+    <row r="2" ht="15.75" spans="2:14">
       <c r="B2" s="1" t="s">
         <v>176</v>
       </c>
@@ -9182,18 +9197,21 @@
       <c r="I2" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="N2" s="2">
         <f>12+Ligma!D5</f>
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="2:13">
+    <row r="3" ht="14.25" spans="2:14">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -9212,18 +9230,21 @@
       <c r="I3" s="12">
         <v>1</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="23">
+        <v>2</v>
+      </c>
+      <c r="K3" s="4">
         <f>ROUNDDOWN(I3/2,0)</f>
         <v>0</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="M3" s="4">
+      <c r="M3" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="N3" s="4">
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="2:13">
+    <row r="4" ht="15.75" spans="2:14">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -9239,21 +9260,24 @@
       <c r="H4" s="16">
         <v>1000</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="24">
         <v>2</v>
       </c>
-      <c r="J4" s="6">
-        <f t="shared" ref="J4:J22" si="0">ROUNDDOWN(I4/2,0)</f>
+      <c r="J4" s="25">
+        <v>3</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" ref="K4:K22" si="0">ROUNDDOWN(I4/2,0)</f>
         <v>1</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="M4" s="8">
+      <c r="M4" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="N4" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:10">
+    <row r="5" ht="15" spans="2:11">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -9266,12 +9290,15 @@
       <c r="I5" s="12">
         <v>3</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="23">
+        <v>3</v>
+      </c>
+      <c r="K5" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="2:10">
+    <row r="6" ht="15" spans="2:11">
       <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
@@ -9281,15 +9308,18 @@
       <c r="H6" s="16">
         <v>6000</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="24">
         <v>4</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="25">
+        <v>4</v>
+      </c>
+      <c r="K6" s="6">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="2:10">
+    <row r="7" ht="14.25" spans="2:11">
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -9302,12 +9332,15 @@
       <c r="I7" s="12">
         <v>5</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="23">
+        <v>4</v>
+      </c>
+      <c r="K7" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="2:10">
+    <row r="8" ht="15.75" spans="2:11">
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
@@ -9317,53 +9350,65 @@
       <c r="H8" s="16">
         <v>15000</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="24">
         <v>6</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="25">
+        <v>5</v>
+      </c>
+      <c r="K8" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="8:10">
+    <row r="9" ht="15" spans="8:11">
       <c r="H9" s="17">
         <v>21000</v>
       </c>
       <c r="I9" s="12">
         <v>7</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="23">
+        <v>7</v>
+      </c>
+      <c r="K9" s="4">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="8:10">
+    <row r="10" ht="15" spans="8:11">
       <c r="H10" s="16">
         <v>28000</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="24">
         <v>8</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="25">
+        <v>8</v>
+      </c>
+      <c r="K10" s="6">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="8:10">
+    <row r="11" ht="15" spans="8:11">
       <c r="H11" s="17">
         <v>36000</v>
       </c>
       <c r="I11" s="12">
         <v>9</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="23">
+        <v>8</v>
+      </c>
+      <c r="K11" s="4">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="15.75" spans="2:10">
+    <row r="12" ht="15.75" spans="2:11">
       <c r="B12" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C12" s="2">
         <f>3+Ligma!D5</f>
@@ -9372,20 +9417,23 @@
       <c r="H12" s="16">
         <v>45000</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="24">
         <v>10</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="25">
+        <v>9</v>
+      </c>
+      <c r="K12" s="6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="2:10">
+    <row r="13" ht="14.25" spans="2:11">
       <c r="B13" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C13" s="4">
-        <f>SUM(M3:M4)</f>
+        <f>SUM(N3:N4)</f>
         <v>5</v>
       </c>
       <c r="H13" s="17">
@@ -9394,46 +9442,55 @@
       <c r="I13" s="12">
         <v>11</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="23">
+        <v>9</v>
+      </c>
+      <c r="K13" s="4">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="2:10">
+    <row r="14" ht="15.75" spans="2:11">
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="H14" s="16">
         <v>66000</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="24">
         <v>12</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="25">
+        <v>10</v>
+      </c>
+      <c r="K14" s="6">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="15.75" spans="8:10">
+    <row r="15" ht="15.75" spans="8:11">
       <c r="H15" s="17">
         <v>78000</v>
       </c>
       <c r="I15" s="12">
         <v>13</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="23">
+        <v>10</v>
+      </c>
+      <c r="K15" s="4">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="16" ht="15.75" spans="2:10">
+    <row r="16" ht="15.75" spans="2:11">
       <c r="B16" s="9" t="s">
         <v>128</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E16" s="18" t="s">
         <v>82</v>
@@ -9441,15 +9498,18 @@
       <c r="H16" s="16">
         <v>91000</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="24">
         <v>14</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="25">
+        <v>11</v>
+      </c>
+      <c r="K16" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="17" ht="15" spans="2:10">
+    <row r="17" ht="15" spans="2:11">
       <c r="B17" s="5" t="s">
         <v>4</v>
       </c>
@@ -9467,12 +9527,15 @@
       <c r="I17" s="12">
         <v>15</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="23">
+        <v>13</v>
+      </c>
+      <c r="K17" s="4">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:10">
+    <row r="18" ht="15" spans="2:11">
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -9487,15 +9550,18 @@
       <c r="H18" s="16">
         <v>120000</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="24">
         <v>16</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="25">
+        <v>14</v>
+      </c>
+      <c r="K18" s="6">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="19" ht="15" spans="2:10">
+    <row r="19" ht="15" spans="2:11">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -9513,12 +9579,15 @@
       <c r="I19" s="12">
         <v>17</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="23">
+        <v>14</v>
+      </c>
+      <c r="K19" s="4">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:10">
+    <row r="20" ht="15" spans="2:11">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
@@ -9535,15 +9604,18 @@
       <c r="H20" s="16">
         <v>153000</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="24">
         <v>18</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="25">
+        <v>15</v>
+      </c>
+      <c r="K20" s="6">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="21" ht="15" spans="2:10">
+    <row r="21" ht="15" spans="2:11">
       <c r="B21" s="5" t="s">
         <v>14</v>
       </c>
@@ -9563,12 +9635,15 @@
       <c r="I21" s="12">
         <v>19</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J21" s="23">
+        <v>15</v>
+      </c>
+      <c r="K21" s="4">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="22" ht="15.75" spans="2:10">
+    <row r="22" ht="15.75" spans="2:11">
       <c r="B22" s="13" t="s">
         <v>16</v>
       </c>
@@ -9583,10 +9658,13 @@
       <c r="H22" s="20">
         <v>190000</v>
       </c>
-      <c r="I22" s="23">
+      <c r="I22" s="26">
         <v>20</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="27">
+        <v>16</v>
+      </c>
+      <c r="K22" s="8">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>

--- a/Fichas/Culto de Nidhogg/Ficha Ligma.xlsx
+++ b/Fichas/Culto de Nidhogg/Ficha Ligma.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ashzi\Documents\GitHub\RPG\Fichas\Culto de Nidhogg\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A93F99E0-F47B-476B-8EF7-CDEED4844877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12315"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ligma" sheetId="1" r:id="rId1"/>
@@ -16,18 +22,31 @@
     <sheet name="Perícias (Cópia)" sheetId="8" state="hidden" r:id="rId7"/>
     <sheet name="uns dados aí" sheetId="4" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Luciano Segundo</author>
     <author/>
   </authors>
   <commentList>
-    <comment ref="D4" authorId="0">
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -53,7 +72,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L4" authorId="1">
+    <comment ref="L4" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -61,13 +80,12 @@
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <scheme val="minor"/>
-            <charset val="0"/>
           </rPr>
           <t>Seu deslocamento é 12m (em vez de 9m).</t>
         </r>
       </text>
     </comment>
-    <comment ref="D5" authorId="0">
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
         <r>
           <rPr>
@@ -92,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L5" authorId="1">
+    <comment ref="L5" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
         <r>
           <rPr>
@@ -100,7 +118,6 @@
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <scheme val="minor"/>
-            <charset val="0"/>
           </rPr>
           <t>Você
 recebe visão na penumbra e +2 em
@@ -108,7 +125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D6" authorId="0">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
         <r>
           <rPr>
@@ -133,7 +150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L6" authorId="1">
+    <comment ref="L6" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
         <r>
           <rPr>
@@ -141,7 +158,6 @@
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <scheme val="minor"/>
-            <charset val="0"/>
           </rPr>
           <t xml:space="preserve">Você recebe
 +1 ponto de mana por nível.
@@ -149,7 +165,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0">
+    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
         <r>
           <rPr>
@@ -174,7 +190,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L7" authorId="0">
+    <comment ref="L7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
         <r>
           <rPr>
@@ -202,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D8" authorId="0">
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
         <r>
           <rPr>
@@ -226,7 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L8" authorId="0">
+    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -262,7 +278,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D9" authorId="0">
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -287,7 +303,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -311,7 +327,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0">
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -336,7 +352,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0">
+    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -361,7 +377,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0">
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-00000F000000}">
       <text>
         <r>
           <rPr>
@@ -391,12 +407,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Luciano Segundo</author>
   </authors>
   <commentList>
-    <comment ref="B3" authorId="0">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -432,7 +448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B4" authorId="0">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -469,7 +485,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B5" authorId="0">
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -503,7 +519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B6" authorId="0">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -542,7 +558,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B7" authorId="0">
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -583,7 +599,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0">
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -643,7 +659,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B9" authorId="0">
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -679,7 +695,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0">
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -718,7 +734,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0">
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -752,7 +768,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B12" authorId="0">
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -792,7 +808,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0">
+    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -860,7 +876,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B14" authorId="0">
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -906,7 +922,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B15" authorId="0">
+    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000D000000}">
       <text>
         <r>
           <rPr>
@@ -935,7 +951,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0">
+    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-00000E000000}">
       <text>
         <r>
           <rPr>
@@ -973,12 +989,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>dopanime</author>
   </authors>
   <commentList>
-    <comment ref="D10" authorId="0">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1582,14 +1598,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;R$&quot;\ * #,##0_-;\-&quot;R$&quot;\ * #,##0_-;_-&quot;R$&quot;\ * &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-  </numFmts>
-  <fonts count="29">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1625,154 +1635,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1798,7 +1663,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1817,194 +1682,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="45">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -2512,253 +2191,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="37" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="40" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="39" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2919,205 +2356,575 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Ênfase 6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Ênfase 6" xfId="2" builtinId="51"/>
-    <cellStyle name="20% - Ênfase 6" xfId="3" builtinId="50"/>
-    <cellStyle name="40% - Ênfase 5" xfId="4" builtinId="47"/>
-    <cellStyle name="Ênfase 5" xfId="5" builtinId="45"/>
-    <cellStyle name="Ênfase 4" xfId="6" builtinId="41"/>
-    <cellStyle name="Título 4" xfId="7" builtinId="19"/>
-    <cellStyle name="60% - Ênfase 3" xfId="8" builtinId="40"/>
-    <cellStyle name="20% - Ênfase 3" xfId="9" builtinId="38"/>
-    <cellStyle name="Ênfase 3" xfId="10" builtinId="37"/>
-    <cellStyle name="Título 3" xfId="11" builtinId="18"/>
-    <cellStyle name="60% - Ênfase 2" xfId="12" builtinId="36"/>
-    <cellStyle name="Célula de Verificação" xfId="13" builtinId="23"/>
-    <cellStyle name="40% - Ênfase 2" xfId="14" builtinId="35"/>
-    <cellStyle name="60% - Ênfase 5" xfId="15" builtinId="48"/>
-    <cellStyle name="Ênfase 2" xfId="16" builtinId="33"/>
-    <cellStyle name="Ênfase 6" xfId="17" builtinId="49"/>
-    <cellStyle name="40% - Ênfase 1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Ênfase 1" xfId="19" builtinId="30"/>
-    <cellStyle name="60% - Ênfase 4" xfId="20" builtinId="44"/>
-    <cellStyle name="Ênfase 1" xfId="21" builtinId="29"/>
-    <cellStyle name="40% - Ênfase 4" xfId="22" builtinId="43"/>
-    <cellStyle name="Ruim" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Ênfase 4" xfId="24" builtinId="42"/>
-    <cellStyle name="Saída" xfId="25" builtinId="21"/>
-    <cellStyle name="Hyperlink seguido" xfId="26" builtinId="9"/>
-    <cellStyle name="Moeda [0]" xfId="27" builtinId="7"/>
-    <cellStyle name="Total" xfId="28" builtinId="25"/>
-    <cellStyle name="Bom" xfId="29" builtinId="26"/>
-    <cellStyle name="40% - Ênfase 3" xfId="30" builtinId="39"/>
-    <cellStyle name="Texto de Aviso" xfId="31" builtinId="11"/>
-    <cellStyle name="Cálculo" xfId="32" builtinId="22"/>
-    <cellStyle name="Entrada" xfId="33" builtinId="20"/>
-    <cellStyle name="Texto Explicativo" xfId="34" builtinId="53"/>
-    <cellStyle name="Título 1" xfId="35" builtinId="16"/>
-    <cellStyle name="Título" xfId="36" builtinId="15"/>
-    <cellStyle name="Observação" xfId="37" builtinId="10"/>
-    <cellStyle name="20% - Ênfase 2" xfId="38" builtinId="34"/>
-    <cellStyle name="60% - Ênfase 1" xfId="39" builtinId="32"/>
-    <cellStyle name="Título 2" xfId="40" builtinId="17"/>
-    <cellStyle name="Hyperlink" xfId="41" builtinId="8"/>
-    <cellStyle name="Célula Vinculada" xfId="42" builtinId="24"/>
-    <cellStyle name="Comma" xfId="43" builtinId="3"/>
-    <cellStyle name="Porcentagem" xfId="44" builtinId="5"/>
-    <cellStyle name="Neutro" xfId="45" builtinId="28"/>
-    <cellStyle name="20% - Ênfase 5" xfId="46" builtinId="46"/>
-    <cellStyle name="Moeda" xfId="47" builtinId="4"/>
-    <cellStyle name="Comma [0]" xfId="48" builtinId="6"/>
   </cellStyles>
   <dxfs count="28">
     <dxf>
       <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="9"/>
         <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -3140,15 +2947,379 @@
     </dxf>
     <dxf>
       <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="9"/>
         <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -3171,48 +3342,15 @@
     </dxf>
     <dxf>
       <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="9"/>
         <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <name val="Palatino Linotype"/>
+        <family val="1"/>
         <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
       <fill>
@@ -3236,15 +3374,48 @@
     </dxf>
     <dxf>
       <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="9"/>
         <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="9"/>
+        <color rgb="FF231F20"/>
+        <name val="Palatino Linotype"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -3267,379 +3438,15 @@
     </dxf>
     <dxf>
       <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="9"/>
         <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
         <name val="Palatino Linotype"/>
+        <family val="1"/>
         <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -3660,436 +3467,93 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Palatino Linotype"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="9"/>
-        <color rgb="FF231F20"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabela2" displayName="Tabela2" ref="B2:E35" totalsRowShown="0">
-  <autoFilter ref="B2:E35"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabela2" displayName="Tabela2" ref="B2:E35" totalsRowShown="0">
+  <autoFilter ref="B2:E35" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="Magia" dataDxfId="0"/>
-    <tableColumn id="4" name="Tipo" dataDxfId="1"/>
-    <tableColumn id="2" name="Círculo" dataDxfId="2"/>
-    <tableColumn id="3" name="Custo" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Magia" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Tipo" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Círculo" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Custo" dataDxfId="24">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(D3,$G$3:$H$7,2,FALSE)^2*10,"")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="B2:M33" totalsRowShown="0">
-  <autoFilter ref="B2:M33"/>
-  <sortState ref="B2:M33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabela1" displayName="Tabela1" ref="B2:M33" totalsRowShown="0">
+  <autoFilter ref="B2:M33" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:M33">
     <sortCondition ref="B2:B33"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" name="Perícia" dataDxfId="4"/>
-    <tableColumn id="11" name="ATR" dataDxfId="5"/>
-    <tableColumn id="2" name="MOD" dataDxfId="6"/>
-    <tableColumn id="3" name="1/2 Nível" dataDxfId="7"/>
-    <tableColumn id="4" name="Treino" dataDxfId="8"/>
-    <tableColumn id="10" name="Raça" dataDxfId="9"/>
-    <tableColumn id="5" name="Bônus" dataDxfId="10"/>
-    <tableColumn id="9" name="Bônus Habilidade" dataDxfId="11"/>
-    <tableColumn id="6" name="Total" dataDxfId="12"/>
-    <tableColumn id="7" name="Treinada?" dataDxfId="13"/>
-    <tableColumn id="12" name="Somente Treinada?" dataDxfId="14"/>
-    <tableColumn id="8" name="Penalidade de Armadura?" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Perícia" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="ATR" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="MOD" dataDxfId="21">
+      <calculatedColumnFormula>VLOOKUP(C3,Ligma!$B$3:$D$8,3,FALSE)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="1/2 Nível" dataDxfId="20">
+      <calculatedColumnFormula>ROUNDDOWN(Ligma!$G$2/2,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Treino" dataDxfId="19">
+      <calculatedColumnFormula>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Raça" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Bônus" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Bônus Habilidade" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Total" dataDxfId="15">
+      <calculatedColumnFormula>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Treinada?" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Somente Treinada?" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Penalidade de Armadura?" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Tabela14" displayName="Tabela14" ref="B2:M33" totalsRowShown="0">
-  <autoFilter ref="B2:M33"/>
-  <sortState ref="B2:M33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabela14" displayName="Tabela14" ref="B2:M33" totalsRowShown="0">
+  <autoFilter ref="B2:M33" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:M33">
     <sortCondition ref="B2:B33"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" name="Perícia" dataDxfId="16"/>
-    <tableColumn id="11" name="ATR" dataDxfId="17"/>
-    <tableColumn id="2" name="MOD" dataDxfId="18"/>
-    <tableColumn id="3" name="1/2 Nível" dataDxfId="19"/>
-    <tableColumn id="4" name="Treino" dataDxfId="20"/>
-    <tableColumn id="10" name="Raça" dataDxfId="21"/>
-    <tableColumn id="5" name="Bônus" dataDxfId="22"/>
-    <tableColumn id="9" name="Bônus Habilidade" dataDxfId="23"/>
-    <tableColumn id="6" name="Total" dataDxfId="24"/>
-    <tableColumn id="7" name="Treinada?" dataDxfId="25"/>
-    <tableColumn id="12" name="Somente Treinada?" dataDxfId="26"/>
-    <tableColumn id="8" name="Penalidade de Armadura?" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Perícia" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="ATR" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="MOD" dataDxfId="9">
+      <calculatedColumnFormula>VLOOKUP(C3,Ligma!$B$3:$D$8,3,FALSE)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="1/2 Nível" dataDxfId="8">
+      <calculatedColumnFormula>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Treino" dataDxfId="7">
+      <calculatedColumnFormula>IF(Tabela14[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0200-00000A000000}" name="Raça" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Bônus" dataDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0200-000009000000}" name="Bônus Habilidade" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Total" dataDxfId="3">
+      <calculatedColumnFormula>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!#REF!,0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Treinada?" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="Somente Treinada?" dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Penalidade de Armadura?" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4367,13 +3831,13 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:N41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:N41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="12.375" customWidth="1"/>
@@ -4386,31 +3850,30 @@
     <col min="14" max="14" width="36.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" customHeight="1" spans="2:14">
-      <c r="B2" s="39" t="s">
+    <row r="2" spans="2:14" ht="15.75" customHeight="1">
+      <c r="B2" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="52"/>
+      <c r="C2" s="82"/>
       <c r="D2" s="40" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="52">
+      <c r="G2" s="82">
         <f>VLOOKUP(G10,'uns dados aí'!$H$2:$I$22,2,TRUE)</f>
         <v>10</v>
       </c>
-      <c r="H2" s="40"/>
-      <c r="K2" s="39" t="s">
+      <c r="H2" s="83"/>
+      <c r="K2" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="40"/>
-    </row>
-    <row r="3" ht="14.25" spans="2:14">
+      <c r="L2" s="82"/>
+      <c r="M2" s="82"/>
+      <c r="N2" s="83"/>
+    </row>
+    <row r="3" spans="2:14" ht="14.25">
       <c r="B3" s="42" t="s">
         <v>4</v>
       </c>
@@ -4446,7 +3909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:14">
+    <row r="4" spans="2:14" ht="15">
       <c r="B4" s="45" t="s">
         <v>9</v>
       </c>
@@ -4476,7 +3939,7 @@
       <c r="M4" s="33"/>
       <c r="N4" s="46"/>
     </row>
-    <row r="5" ht="14.25" spans="2:14">
+    <row r="5" spans="2:14" ht="14.25">
       <c r="B5" s="42" t="s">
         <v>10</v>
       </c>
@@ -4491,11 +3954,11 @@
       <c r="F5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="84">
         <f>10+D4+C16</f>
         <v>15</v>
       </c>
-      <c r="H5" s="92"/>
+      <c r="H5" s="85"/>
       <c r="K5" s="42">
         <v>2</v>
       </c>
@@ -4503,26 +3966,26 @@
       <c r="M5" s="31"/>
       <c r="N5" s="43"/>
     </row>
-    <row r="6" ht="15" spans="2:14">
+    <row r="6" spans="2:14" ht="15">
       <c r="B6" s="45" t="s">
         <v>12</v>
       </c>
       <c r="C6" s="33">
         <f>'uns dados aí'!C6+(VLOOKUP(B6,Perícias!$O$7:$P$13,2,FALSE))</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="46">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="44">
+      <c r="G6" s="95">
         <f>G5+Perícias!J12</f>
         <v>21</v>
       </c>
-      <c r="H6" s="93"/>
+      <c r="H6" s="96"/>
       <c r="K6" s="45">
         <v>3</v>
       </c>
@@ -4530,7 +3993,7 @@
       <c r="M6" s="33"/>
       <c r="N6" s="46"/>
     </row>
-    <row r="7" ht="14.25" spans="2:14">
+    <row r="7" spans="2:14" ht="14.25">
       <c r="B7" s="42" t="s">
         <v>14</v>
       </c>
@@ -4545,11 +4008,11 @@
       <c r="F7" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="84">
         <f>Perícias!J27+Perícias!J21</f>
-        <v>37</v>
-      </c>
-      <c r="H7" s="92"/>
+        <v>27</v>
+      </c>
+      <c r="H7" s="85"/>
       <c r="K7" s="42">
         <v>4</v>
       </c>
@@ -4557,11 +4020,11 @@
       <c r="M7" s="31"/>
       <c r="N7" s="43"/>
     </row>
-    <row r="8" ht="15.75" spans="2:14">
+    <row r="8" spans="2:14" ht="15">
       <c r="B8" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="56">
+      <c r="C8" s="54">
         <f>'uns dados aí'!C8+(VLOOKUP(B8,Perícias!$O$7:$P$13,2,FALSE))</f>
         <v>14</v>
       </c>
@@ -4572,10 +4035,10 @@
       <c r="F8" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="94">
+      <c r="G8" s="86">
         <v>0.5</v>
       </c>
-      <c r="H8" s="95"/>
+      <c r="H8" s="87"/>
       <c r="K8" s="45">
         <v>5</v>
       </c>
@@ -4583,12 +4046,12 @@
       <c r="M8" s="33"/>
       <c r="N8" s="46"/>
     </row>
-    <row r="9" ht="15" spans="6:14">
+    <row r="9" spans="2:14" ht="14.25">
       <c r="F9" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="31"/>
-      <c r="H9" s="43"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="89"/>
       <c r="K9" s="42">
         <v>6</v>
       </c>
@@ -4596,14 +4059,14 @@
       <c r="M9" s="31"/>
       <c r="N9" s="43"/>
     </row>
-    <row r="10" ht="15.75" spans="6:14">
+    <row r="10" spans="2:14" ht="15">
       <c r="F10" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="56">
+      <c r="G10" s="90">
         <v>45000</v>
       </c>
-      <c r="H10" s="50"/>
+      <c r="H10" s="91"/>
       <c r="K10" s="45">
         <v>7</v>
       </c>
@@ -4611,7 +4074,7 @@
       <c r="M10" s="33"/>
       <c r="N10" s="46"/>
     </row>
-    <row r="11" ht="15.75" spans="11:14">
+    <row r="11" spans="2:14" ht="14.25">
       <c r="K11" s="42">
         <v>8</v>
       </c>
@@ -4619,17 +4082,17 @@
       <c r="M11" s="31"/>
       <c r="N11" s="43"/>
     </row>
-    <row r="12" ht="16.5" spans="2:14">
-      <c r="B12" s="75" t="s">
+    <row r="12" spans="2:14" ht="15">
+      <c r="B12" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="76"/>
-      <c r="D12" s="76"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="77"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="94"/>
       <c r="K12" s="45">
         <v>9</v>
       </c>
@@ -4637,8 +4100,8 @@
       <c r="M12" s="33"/>
       <c r="N12" s="46"/>
     </row>
-    <row r="13" ht="15.75" spans="2:14">
-      <c r="B13" s="91"/>
+    <row r="13" spans="2:14" ht="14.25">
+      <c r="B13" s="78"/>
       <c r="K13" s="42">
         <v>10</v>
       </c>
@@ -4646,18 +4109,18 @@
       <c r="M13" s="31"/>
       <c r="N13" s="43"/>
     </row>
-    <row r="14" ht="15.75" spans="2:14">
-      <c r="B14" s="39" t="s">
+    <row r="14" spans="2:14" ht="15">
+      <c r="B14" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="52"/>
-      <c r="D14" s="40"/>
-      <c r="F14" s="39" t="s">
+      <c r="C14" s="82"/>
+      <c r="D14" s="83"/>
+      <c r="F14" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="40"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="83"/>
       <c r="K14" s="45">
         <v>11</v>
       </c>
@@ -4665,7 +4128,7 @@
       <c r="M14" s="33"/>
       <c r="N14" s="46"/>
     </row>
-    <row r="15" ht="14.25" spans="2:14">
+    <row r="15" spans="2:14" ht="14.25">
       <c r="B15" s="42" t="s">
         <v>23</v>
       </c>
@@ -4694,11 +4157,11 @@
       <c r="M15" s="31"/>
       <c r="N15" s="43"/>
     </row>
-    <row r="16" ht="30.75" spans="2:14">
+    <row r="16" spans="2:14" ht="30">
       <c r="B16" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="56">
+      <c r="C16" s="54">
         <f>IFERROR(VLOOKUP($B$16,Inventário!$B$3:$E$5,2,FALSE),"")</f>
         <v>2</v>
       </c>
@@ -4709,11 +4172,11 @@
       <c r="F16" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="56" t="str">
+      <c r="G16" s="54" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$E$13,2,FALSE),"")</f>
         <v>3d6+2</v>
       </c>
-      <c r="H16" s="56" t="str">
+      <c r="H16" s="54" t="str">
         <f>IFERROR(VLOOKUP($F$16,Inventário!$B$8:$E$13,3,FALSE),"")</f>
         <v>Abrir nota</v>
       </c>
@@ -4728,7 +4191,7 @@
       <c r="M16" s="33"/>
       <c r="N16" s="46"/>
     </row>
-    <row r="17" ht="15" spans="11:14">
+    <row r="17" spans="11:14" ht="14.25">
       <c r="K17" s="42">
         <v>14</v>
       </c>
@@ -4736,7 +4199,7 @@
       <c r="M17" s="31"/>
       <c r="N17" s="43"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="11:14">
+    <row r="18" spans="11:14" ht="15.75" customHeight="1">
       <c r="K18" s="45">
         <v>15</v>
       </c>
@@ -4744,7 +4207,7 @@
       <c r="M18" s="33"/>
       <c r="N18" s="46"/>
     </row>
-    <row r="19" ht="14.25" spans="11:14">
+    <row r="19" spans="11:14" ht="14.25">
       <c r="K19" s="42">
         <v>16</v>
       </c>
@@ -4752,7 +4215,7 @@
       <c r="M19" s="31"/>
       <c r="N19" s="43"/>
     </row>
-    <row r="20" ht="15" spans="11:14">
+    <row r="20" spans="11:14" ht="15">
       <c r="K20" s="45">
         <v>17</v>
       </c>
@@ -4760,7 +4223,7 @@
       <c r="M20" s="33"/>
       <c r="N20" s="46"/>
     </row>
-    <row r="21" ht="14.25" spans="11:14">
+    <row r="21" spans="11:14" ht="14.25">
       <c r="K21" s="42">
         <v>18</v>
       </c>
@@ -4768,34 +4231,32 @@
       <c r="M21" s="31"/>
       <c r="N21" s="43"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="11:14">
+    <row r="22" spans="11:14" ht="15.75" customHeight="1">
       <c r="K22" s="49">
         <v>20</v>
       </c>
-      <c r="L22" s="56"/>
-      <c r="M22" s="56"/>
+      <c r="L22" s="54"/>
+      <c r="M22" s="54"/>
       <c r="N22" s="50"/>
     </row>
-    <row r="23" ht="15"/>
-    <row r="24" ht="15.75" spans="11:12">
-      <c r="K24" s="39" t="s">
+    <row r="24" spans="11:14" ht="15">
+      <c r="K24" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="L24" s="40"/>
-    </row>
-    <row r="25" ht="14.25" spans="11:12">
+      <c r="L24" s="83"/>
+    </row>
+    <row r="25" spans="11:14" ht="14.25">
       <c r="K25" s="42" t="s">
         <v>5</v>
       </c>
       <c r="L25" s="43"/>
     </row>
-    <row r="26" ht="15.75" spans="11:12">
+    <row r="26" spans="11:14" ht="15">
       <c r="K26" s="49" t="s">
         <v>7</v>
       </c>
       <c r="L26" s="50"/>
     </row>
-    <row r="27" ht="14.25"/>
     <row r="41" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
@@ -4804,32 +4265,40 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G6:H6"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:I14"/>
+    <mergeCell ref="K24:L24"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:I14"/>
-    <mergeCell ref="K24:L24"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F16">
-      <formula1>Inventário!$B$9:$B$13</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16">
-      <formula1>Inventário!$B$4:$B$5</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <headerFooter/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
+          <x14:formula1>
+            <xm:f>Inventário!$B$9:$B$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>F16</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+          <x14:formula1>
+            <xm:f>Inventário!$B$4:$B$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>B16</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:O23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="12" max="12" width="19.75" customWidth="1"/>
@@ -4837,342 +4306,340 @@
     <col min="14" max="14" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:15">
-      <c r="A1" s="75" t="s">
+    <row r="1" spans="1:15" ht="15">
+      <c r="A1" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="77"/>
-      <c r="I1" s="75" t="s">
+      <c r="B1" s="93"/>
+      <c r="C1" s="93"/>
+      <c r="D1" s="93"/>
+      <c r="E1" s="93"/>
+      <c r="F1" s="93"/>
+      <c r="G1" s="94"/>
+      <c r="I1" s="92" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="76"/>
-      <c r="K1" s="76"/>
-      <c r="L1" s="76"/>
-      <c r="M1" s="76"/>
-      <c r="N1" s="76"/>
-      <c r="O1" s="77"/>
-    </row>
-    <row r="2" ht="15"/>
-    <row r="3" ht="15.75" spans="2:13">
-      <c r="B3" s="39" t="s">
+      <c r="J1" s="93"/>
+      <c r="K1" s="93"/>
+      <c r="L1" s="93"/>
+      <c r="M1" s="93"/>
+      <c r="N1" s="93"/>
+      <c r="O1" s="94"/>
+    </row>
+    <row r="3" spans="1:15" ht="15">
+      <c r="B3" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52" t="s">
+      <c r="C3" s="82"/>
+      <c r="D3" s="82" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="52"/>
+      <c r="E3" s="82"/>
       <c r="F3" s="40"/>
-      <c r="K3" s="78" t="s">
+      <c r="K3" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="79" t="s">
+      <c r="L3" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="M3" s="87" t="s">
+      <c r="M3" s="74" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" spans="2:13">
-      <c r="B4" s="42" t="s">
+    <row r="4" spans="1:15" ht="15" customHeight="1">
+      <c r="B4" s="97" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31" t="s">
+      <c r="C4" s="88"/>
+      <c r="D4" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="31"/>
+      <c r="E4" s="88"/>
       <c r="F4" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="80" t="s">
+      <c r="K4" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="81" t="s">
+      <c r="L4" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="M4" s="88" t="s">
+      <c r="M4" s="75" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="2:13">
-      <c r="B5" s="45" t="s">
+    <row r="5" spans="1:15" ht="15" customHeight="1">
+      <c r="B5" s="98" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33" t="s">
+      <c r="C5" s="99"/>
+      <c r="D5" s="99" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="33"/>
+      <c r="E5" s="99"/>
       <c r="F5" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="82" t="s">
+      <c r="K5" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="83" t="s">
+      <c r="L5" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="M5" s="96" t="s">
+      <c r="M5" s="79" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" spans="2:13">
-      <c r="B6" s="42" t="s">
+    <row r="6" spans="1:15" ht="15" customHeight="1">
+      <c r="B6" s="97" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31" t="s">
+      <c r="C6" s="88"/>
+      <c r="D6" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="31"/>
+      <c r="E6" s="88"/>
       <c r="F6" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="80" t="s">
+      <c r="K6" s="67" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="81" t="s">
+      <c r="L6" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="97" t="s">
+      <c r="M6" s="80" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="2:13">
-      <c r="B7" s="45" t="s">
+    <row r="7" spans="1:15" ht="15">
+      <c r="B7" s="98" t="s">
         <v>52</v>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33" t="s">
+      <c r="C7" s="99"/>
+      <c r="D7" s="99" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="33"/>
+      <c r="E7" s="99"/>
       <c r="F7" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="82" t="s">
+      <c r="K7" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="83" t="s">
+      <c r="L7" s="70" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="89"/>
-    </row>
-    <row r="8" ht="14.25" spans="2:13">
-      <c r="B8" s="42" t="s">
+      <c r="M7" s="76"/>
+    </row>
+    <row r="8" spans="1:15" ht="14.25">
+      <c r="B8" s="97" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31" t="s">
+      <c r="C8" s="88"/>
+      <c r="D8" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="31"/>
+      <c r="E8" s="88"/>
       <c r="F8" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="80" t="s">
+      <c r="K8" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="L8" s="84" t="s">
+      <c r="L8" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="M8" s="88"/>
-    </row>
-    <row r="9" ht="15" spans="2:13">
-      <c r="B9" s="45" t="s">
+      <c r="M8" s="75"/>
+    </row>
+    <row r="9" spans="1:15" ht="15">
+      <c r="B9" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33" t="s">
+      <c r="C9" s="99"/>
+      <c r="D9" s="99" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="33"/>
+      <c r="E9" s="99"/>
       <c r="F9" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="82"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="89"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" spans="2:13">
-      <c r="B10" s="42" t="s">
+      <c r="K9" s="69"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="76"/>
+    </row>
+    <row r="10" spans="1:15" ht="15" customHeight="1">
+      <c r="B10" s="97" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31" t="s">
+      <c r="C10" s="88"/>
+      <c r="D10" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="31"/>
+      <c r="E10" s="88"/>
       <c r="F10" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K10" s="80"/>
-      <c r="L10" s="81"/>
-      <c r="M10" s="88"/>
-    </row>
-    <row r="11" ht="15" spans="2:13">
-      <c r="B11" s="45" t="s">
+      <c r="K10" s="67"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="75"/>
+    </row>
+    <row r="11" spans="1:15" ht="15">
+      <c r="B11" s="98" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33" t="s">
+      <c r="C11" s="99"/>
+      <c r="D11" s="99" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="33"/>
+      <c r="E11" s="99"/>
       <c r="F11" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="82"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="89"/>
-    </row>
-    <row r="12" ht="14.25" spans="2:13">
-      <c r="B12" s="42" t="s">
+      <c r="K11" s="69"/>
+      <c r="L11" s="70"/>
+      <c r="M11" s="76"/>
+    </row>
+    <row r="12" spans="1:15" ht="14.25">
+      <c r="B12" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31" t="s">
+      <c r="C12" s="88"/>
+      <c r="D12" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="31"/>
+      <c r="E12" s="88"/>
       <c r="F12" s="43" t="s">
         <v>40</v>
       </c>
-      <c r="K12" s="80"/>
-      <c r="L12" s="81"/>
-      <c r="M12" s="88"/>
-    </row>
-    <row r="13" ht="15" spans="2:13">
-      <c r="B13" s="45" t="s">
+      <c r="K12" s="67"/>
+      <c r="L12" s="68"/>
+      <c r="M12" s="75"/>
+    </row>
+    <row r="13" spans="1:15" ht="15">
+      <c r="B13" s="98" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33" t="s">
+      <c r="C13" s="99"/>
+      <c r="D13" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="E13" s="33"/>
+      <c r="E13" s="99"/>
       <c r="F13" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="K13" s="82"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="89"/>
-    </row>
-    <row r="14" ht="14.25" spans="2:13">
-      <c r="B14" s="42" t="s">
+      <c r="K13" s="69"/>
+      <c r="L13" s="70"/>
+      <c r="M13" s="76"/>
+    </row>
+    <row r="14" spans="1:15" ht="14.25">
+      <c r="B14" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="88"/>
+      <c r="E14" s="88"/>
       <c r="F14" s="43"/>
-      <c r="K14" s="80"/>
-      <c r="L14" s="81"/>
-      <c r="M14" s="88"/>
-    </row>
-    <row r="15" ht="15" spans="2:13">
-      <c r="B15" s="45" t="s">
+      <c r="K14" s="67"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="75"/>
+    </row>
+    <row r="15" spans="1:15" ht="15">
+      <c r="B15" s="98" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
       <c r="F15" s="46"/>
-      <c r="K15" s="82"/>
-      <c r="L15" s="83"/>
-      <c r="M15" s="89"/>
-    </row>
-    <row r="16" ht="14.25" spans="2:13">
-      <c r="B16" s="42" t="s">
+      <c r="K15" s="69"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="76"/>
+    </row>
+    <row r="16" spans="1:15" ht="14.25">
+      <c r="B16" s="97" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
       <c r="F16" s="43"/>
-      <c r="K16" s="80"/>
-      <c r="L16" s="81"/>
-      <c r="M16" s="88"/>
-    </row>
-    <row r="17" ht="15" spans="2:13">
-      <c r="B17" s="45" t="s">
+      <c r="K16" s="67"/>
+      <c r="L16" s="68"/>
+      <c r="M16" s="75"/>
+    </row>
+    <row r="17" spans="2:13" ht="15">
+      <c r="B17" s="98" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
       <c r="F17" s="46"/>
-      <c r="K17" s="82"/>
-      <c r="L17" s="83"/>
-      <c r="M17" s="89"/>
-    </row>
-    <row r="18" ht="14.25" spans="2:13">
-      <c r="B18" s="42" t="s">
+      <c r="K17" s="69"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="76"/>
+    </row>
+    <row r="18" spans="2:13" ht="14.25">
+      <c r="B18" s="97" t="s">
         <v>75</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="88"/>
       <c r="F18" s="43"/>
-      <c r="K18" s="80"/>
-      <c r="L18" s="81"/>
-      <c r="M18" s="88"/>
-    </row>
-    <row r="19" ht="15" spans="2:13">
-      <c r="B19" s="45" t="s">
+      <c r="K18" s="67"/>
+      <c r="L18" s="68"/>
+      <c r="M18" s="75"/>
+    </row>
+    <row r="19" spans="2:13" ht="15">
+      <c r="B19" s="98" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="33"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
       <c r="F19" s="46"/>
-      <c r="K19" s="82"/>
-      <c r="L19" s="83"/>
-      <c r="M19" s="89"/>
-    </row>
-    <row r="20" ht="14.25" spans="2:13">
-      <c r="B20" s="42" t="s">
+      <c r="K19" s="69"/>
+      <c r="L19" s="70"/>
+      <c r="M19" s="76"/>
+    </row>
+    <row r="20" spans="2:13" ht="14.25">
+      <c r="B20" s="97" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="88"/>
       <c r="F20" s="43"/>
-      <c r="K20" s="80"/>
-      <c r="L20" s="81"/>
-      <c r="M20" s="88"/>
-    </row>
-    <row r="21" ht="15" spans="2:13">
-      <c r="B21" s="45" t="s">
+      <c r="K20" s="67"/>
+      <c r="L20" s="68"/>
+      <c r="M20" s="75"/>
+    </row>
+    <row r="21" spans="2:13" ht="15">
+      <c r="B21" s="98" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
       <c r="F21" s="46"/>
-      <c r="K21" s="82"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="89"/>
-    </row>
-    <row r="22" ht="15" spans="2:13">
-      <c r="B22" s="47" t="s">
+      <c r="K21" s="69"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="76"/>
+    </row>
+    <row r="22" spans="2:13" ht="14.25">
+      <c r="B22" s="100" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
+      <c r="C22" s="101"/>
+      <c r="D22" s="101"/>
+      <c r="E22" s="101"/>
       <c r="F22" s="48"/>
-      <c r="K22" s="85"/>
-      <c r="L22" s="86"/>
-      <c r="M22" s="90"/>
-    </row>
-    <row r="23" ht="14.25"/>
+      <c r="K22" s="72"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="77"/>
+    </row>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="A1:G1"/>
@@ -5218,24 +4685,21 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="D22:E22"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:H32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="B2:H31"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.875" customWidth="1"/>
     <col min="7" max="7" width="8.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:8">
+    <row r="2" spans="2:8" ht="15">
       <c r="B2" s="39" t="s">
         <v>0</v>
       </c>
@@ -5248,12 +4712,12 @@
       <c r="E2" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="H2" s="69"/>
-    </row>
-    <row r="3" ht="15" spans="2:8">
+      <c r="H2" s="103"/>
+    </row>
+    <row r="3" spans="2:8" ht="14.25">
       <c r="B3" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Acrobacia</v>
@@ -5264,21 +4728,21 @@
       </c>
       <c r="D3" s="31">
         <f ca="1">RANDBETWEEN(1,20)</f>
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E3" s="43">
         <f ca="1">SUM(C3:D3)</f>
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G3" s="47" t="s">
         <v>83</v>
       </c>
       <c r="H3" s="48">
         <f ca="1">VLOOKUP(G3,B2:E31,4,FALSE)</f>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" spans="2:5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="15">
       <c r="B4" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Adestramento</v>
@@ -5288,15 +4752,15 @@
         <v>7</v>
       </c>
       <c r="D4" s="33">
-        <f ca="1" t="shared" ref="D4:D31" si="0">RANDBETWEEN(1,20)</f>
-        <v>10</v>
+        <f t="shared" ref="D4:D31" ca="1" si="0">RANDBETWEEN(1,20)</f>
+        <v>2</v>
       </c>
       <c r="E4" s="46">
-        <f ca="1" t="shared" ref="E4:E31" si="1">SUM(C4:D4)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" spans="2:5">
+        <f t="shared" ref="E4:E31" ca="1" si="1">SUM(C4:D4)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="14.25">
       <c r="B5" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atletismo</v>
@@ -5306,15 +4770,15 @@
         <v>8</v>
       </c>
       <c r="D5" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>4</v>
       </c>
       <c r="E5" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" ht="15" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="15">
       <c r="B6" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Atuação</v>
@@ -5324,15 +4788,15 @@
         <v>7</v>
       </c>
       <c r="D6" s="33">
-        <f ca="1" t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="E6" s="46">
+        <f t="shared" ca="1" si="1"/>
         <v>14</v>
       </c>
-      <c r="E6" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" ht="14.25" spans="2:5">
+    </row>
+    <row r="7" spans="2:8" ht="14.25">
       <c r="B7" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Cavalgar</v>
@@ -5342,51 +4806,51 @@
         <v>8</v>
       </c>
       <c r="D7" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>8</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
       </c>
       <c r="E7" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" ht="15" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="15">
       <c r="B8" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Conhecimento</v>
       </c>
       <c r="C8" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
+        <v>14</v>
+      </c>
+      <c r="D8" s="33">
+        <f t="shared" ca="1" si="0"/>
         <v>20</v>
       </c>
-      <c r="D8" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>1</v>
-      </c>
       <c r="E8" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" ht="14.25" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="14.25">
       <c r="B9" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Cura</v>
       </c>
       <c r="C9" s="31">
         <f>Tabela1[[#This Row],[Total]]</f>
+        <v>9</v>
+      </c>
+      <c r="D9" s="31">
+        <f t="shared" ca="1" si="0"/>
         <v>18</v>
       </c>
-      <c r="D9" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
-      </c>
       <c r="E9" s="43">
-        <f ca="1" t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>27</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="2:5">
+    <row r="10" spans="2:8" ht="15">
       <c r="B10" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Diplomacia</v>
@@ -5396,15 +4860,15 @@
         <v>7</v>
       </c>
       <c r="D10" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>12</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
       </c>
       <c r="E10" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" ht="14.25" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="14.25">
       <c r="B11" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Enganação</v>
@@ -5414,15 +4878,15 @@
         <v>7</v>
       </c>
       <c r="D11" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
       </c>
       <c r="E11" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" ht="15">
       <c r="B12" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Fortitude</v>
@@ -5432,15 +4896,15 @@
         <v>6</v>
       </c>
       <c r="D12" s="33">
-        <f ca="1" t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>6</v>
       </c>
       <c r="E12" s="46">
-        <f ca="1" t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>12</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="2:5">
+    <row r="13" spans="2:8" ht="14.25">
       <c r="B13" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Furtividade</v>
@@ -5450,33 +4914,33 @@
         <v>8</v>
       </c>
       <c r="D13" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>5</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
       </c>
       <c r="E13" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" ht="15" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" ht="15">
       <c r="B14" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Guerra</v>
       </c>
       <c r="C14" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
+        <v>16</v>
+      </c>
+      <c r="D14" s="33">
+        <f t="shared" ca="1" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E14" s="46">
+        <f t="shared" ca="1" si="1"/>
         <v>22</v>
       </c>
-      <c r="D14" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E14" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" ht="14.25" spans="2:5">
+    </row>
+    <row r="15" spans="2:8" ht="14.25">
       <c r="B15" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Iniciativa</v>
@@ -5486,15 +4950,15 @@
         <v>8</v>
       </c>
       <c r="D15" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
       </c>
       <c r="E15" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" ht="15" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" ht="15">
       <c r="B16" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Intimidação</v>
@@ -5504,15 +4968,15 @@
         <v>7</v>
       </c>
       <c r="D16" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>13</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>10</v>
       </c>
       <c r="E16" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" ht="14.25" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="14.25">
       <c r="B17" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Intuição</v>
@@ -5522,33 +4986,33 @@
         <v>9</v>
       </c>
       <c r="D17" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
       </c>
       <c r="E17" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" ht="15" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="15">
       <c r="B18" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Investigação</v>
       </c>
       <c r="C18" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D18" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>19</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
       </c>
       <c r="E18" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="14.25">
       <c r="B19" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Jogatina</v>
@@ -5558,15 +5022,15 @@
         <v>7</v>
       </c>
       <c r="D19" s="31">
-        <f ca="1" t="shared" si="0"/>
+        <f t="shared" ca="1" si="0"/>
         <v>7</v>
       </c>
       <c r="E19" s="43">
-        <f ca="1" t="shared" si="1"/>
+        <f t="shared" ca="1" si="1"/>
         <v>14</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:5">
+    <row r="20" spans="2:5" ht="15">
       <c r="B20" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ladinagem</v>
@@ -5576,141 +5040,141 @@
         <v>8</v>
       </c>
       <c r="D20" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>16</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>15</v>
       </c>
       <c r="E20" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="14.25">
       <c r="B21" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Luta</v>
       </c>
       <c r="C21" s="31">
         <f>Tabela1[[#This Row],[Total]]</f>
+        <v>12</v>
+      </c>
+      <c r="D21" s="31">
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E21" s="43">
+        <f t="shared" ca="1" si="1"/>
         <v>17</v>
       </c>
-      <c r="D21" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E21" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" ht="15" spans="2:5">
+    </row>
+    <row r="22" spans="2:5" ht="15">
       <c r="B22" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Misticismo</v>
       </c>
       <c r="C22" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D22" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>6</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
       </c>
       <c r="E22" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="14.25">
       <c r="B23" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Nobreza</v>
       </c>
       <c r="C23" s="31">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>9</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>5</v>
       </c>
       <c r="E23" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" ht="30" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="30">
       <c r="B24" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Alquimista)</v>
       </c>
       <c r="C24" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D24" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>4</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>3</v>
       </c>
       <c r="E24" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="14.25">
       <c r="B25" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Armeiro)</v>
       </c>
       <c r="C25" s="31">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D25" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
       </c>
       <c r="E25" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" ht="30" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="30">
       <c r="B26" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Ofício (Engenhoqueiro)</v>
       </c>
       <c r="C26" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D26" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
       </c>
       <c r="E26" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" ht="14.25" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="14.25">
       <c r="B27" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Percepção</v>
       </c>
       <c r="C27" s="31">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D27" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>2</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
       </c>
       <c r="E27" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="15">
       <c r="B28" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Pilotagem</v>
@@ -5720,88 +5184,85 @@
         <v>8</v>
       </c>
       <c r="D28" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>17</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
       </c>
       <c r="E28" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" ht="14.25" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="14.25">
       <c r="B29" s="42" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Pontaria</v>
       </c>
       <c r="C29" s="31">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D29" s="31">
-        <f ca="1" t="shared" si="0"/>
-        <v>1</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
       </c>
       <c r="E29" s="43">
-        <f ca="1" t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="30" ht="15" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="15">
       <c r="B30" s="45" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Reflexos</v>
       </c>
       <c r="C30" s="33">
         <f>Tabela1[[#This Row],[Total]]</f>
+        <v>12</v>
+      </c>
+      <c r="D30" s="33">
+        <f t="shared" ca="1" si="0"/>
         <v>17</v>
       </c>
-      <c r="D30" s="33">
-        <f ca="1" t="shared" si="0"/>
-        <v>5</v>
-      </c>
       <c r="E30" s="46">
-        <f ca="1" t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" ht="15" spans="2:5">
+        <f t="shared" ca="1" si="1"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="14.25">
       <c r="B31" s="47" t="str">
         <f>Tabela1[[#This Row],[Perícia]]</f>
         <v>Religião</v>
       </c>
       <c r="C31" s="53">
         <f>Tabela1[[#This Row],[Total]]</f>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D31" s="53">
-        <f ca="1" t="shared" si="0"/>
-        <v>12</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>7</v>
       </c>
       <c r="E31" s="48">
-        <f ca="1" t="shared" si="1"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" ht="14.25"/>
+        <f t="shared" ca="1" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="G2:H2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>$B$2:$B$31</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <headerFooter/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A2:H35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="23.25" customWidth="1"/>
     <col min="3" max="3" width="15.375" customWidth="1"/>
@@ -5809,8 +5270,7 @@
     <col min="5" max="5" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:8">
+    <row r="2" spans="1:8" ht="15">
       <c r="B2" s="28" t="s">
         <v>84</v>
       </c>
@@ -5820,22 +5280,22 @@
       <c r="D2" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="74" t="s">
+      <c r="E2" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="81" t="s">
         <v>87</v>
       </c>
-      <c r="H2" s="40"/>
-    </row>
-    <row r="3" ht="14.25" spans="1:8">
+      <c r="H2" s="83"/>
+    </row>
+    <row r="3" spans="1:8" ht="14.25">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="62" t="s">
         <v>89</v>
       </c>
       <c r="D3" s="31">
@@ -5852,7 +5312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="1:8">
+    <row r="4" spans="1:8" ht="15">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5876,11 +5336,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="1:8">
+    <row r="5" spans="1:8" ht="14.25">
       <c r="A5">
         <v>1</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="62" t="s">
         <v>91</v>
       </c>
       <c r="C5" s="30" t="s">
@@ -5900,7 +5360,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="1:8">
+    <row r="6" spans="1:8" ht="15">
       <c r="A6">
         <v>2</v>
       </c>
@@ -5924,11 +5384,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="15" spans="1:8">
+    <row r="7" spans="1:8" ht="14.25">
       <c r="A7">
         <v>3</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="62" t="s">
         <v>94</v>
       </c>
       <c r="C7" s="30" t="s">
@@ -5948,7 +5408,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="1:5">
+    <row r="8" spans="1:8" ht="15">
       <c r="A8">
         <v>4</v>
       </c>
@@ -5966,11 +5426,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:5">
+    <row r="9" spans="1:8" ht="14.25">
       <c r="A9">
         <v>5</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="62" t="s">
         <v>96</v>
       </c>
       <c r="C9" s="30" t="s">
@@ -5984,7 +5444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="1:5">
+    <row r="10" spans="1:8" ht="15">
       <c r="A10">
         <v>6</v>
       </c>
@@ -6002,11 +5462,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="1:5">
+    <row r="11" spans="1:8" ht="14.25">
       <c r="A11">
         <v>7</v>
       </c>
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="62" t="s">
         <v>98</v>
       </c>
       <c r="C11" s="30" t="s">
@@ -6020,7 +5480,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="1:5">
+    <row r="12" spans="1:8" ht="15">
       <c r="A12">
         <v>8</v>
       </c>
@@ -6038,11 +5498,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="1:5">
+    <row r="13" spans="1:8" ht="14.25">
       <c r="A13">
         <v>9</v>
       </c>
-      <c r="B13" s="72" t="s">
+      <c r="B13" s="62" t="s">
         <v>100</v>
       </c>
       <c r="C13" s="30" t="s">
@@ -6056,7 +5516,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" ht="15" spans="1:5">
+    <row r="14" spans="1:8" ht="15">
       <c r="A14">
         <v>10</v>
       </c>
@@ -6074,11 +5534,11 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="1:5">
+    <row r="15" spans="1:8" ht="14.25">
       <c r="A15">
         <v>10</v>
       </c>
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="62" t="s">
         <v>102</v>
       </c>
       <c r="C15" s="30" t="s">
@@ -6092,7 +5552,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" ht="15" spans="2:5">
+    <row r="16" spans="1:8" ht="15">
       <c r="B16" s="34" t="s">
         <v>104</v>
       </c>
@@ -6107,8 +5567,8 @@
         <v>360</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="2:5">
-      <c r="B17" s="72"/>
+    <row r="17" spans="2:5" ht="14.25">
+      <c r="B17" s="62"/>
       <c r="C17" s="30"/>
       <c r="D17" s="31"/>
       <c r="E17" s="41" t="str">
@@ -6116,7 +5576,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:5">
+    <row r="18" spans="2:5" ht="15">
       <c r="B18" s="34"/>
       <c r="C18" s="32"/>
       <c r="D18" s="33"/>
@@ -6125,8 +5585,8 @@
         <v/>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="2:5">
-      <c r="B19" s="72"/>
+    <row r="19" spans="2:5" ht="14.25">
+      <c r="B19" s="62"/>
       <c r="C19" s="30"/>
       <c r="D19" s="31"/>
       <c r="E19" s="41" t="str">
@@ -6134,7 +5594,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:5">
+    <row r="20" spans="2:5" ht="15">
       <c r="B20" s="34"/>
       <c r="C20" s="32"/>
       <c r="D20" s="33"/>
@@ -6143,8 +5603,8 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="2:5">
-      <c r="B21" s="72"/>
+    <row r="21" spans="2:5" ht="14.25">
+      <c r="B21" s="62"/>
       <c r="C21" s="30"/>
       <c r="D21" s="31"/>
       <c r="E21" s="41" t="str">
@@ -6152,7 +5612,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" spans="2:5">
+    <row r="22" spans="2:5" ht="15">
       <c r="B22" s="34"/>
       <c r="C22" s="32"/>
       <c r="D22" s="33"/>
@@ -6161,8 +5621,8 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="14.25" spans="2:5">
-      <c r="B23" s="72"/>
+    <row r="23" spans="2:5" ht="14.25">
+      <c r="B23" s="62"/>
       <c r="C23" s="30"/>
       <c r="D23" s="31"/>
       <c r="E23" s="41" t="str">
@@ -6170,7 +5630,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" spans="2:5">
+    <row r="24" spans="2:5" ht="15">
       <c r="B24" s="34"/>
       <c r="C24" s="32"/>
       <c r="D24" s="33"/>
@@ -6179,8 +5639,8 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="2:5">
-      <c r="B25" s="72"/>
+    <row r="25" spans="2:5" ht="14.25">
+      <c r="B25" s="62"/>
       <c r="C25" s="30"/>
       <c r="D25" s="31"/>
       <c r="E25" s="41" t="str">
@@ -6188,7 +5648,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" spans="2:5">
+    <row r="26" spans="2:5" ht="15">
       <c r="B26" s="34"/>
       <c r="C26" s="34"/>
       <c r="D26" s="33"/>
@@ -6197,8 +5657,8 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="14.25" spans="2:5">
-      <c r="B27" s="72"/>
+    <row r="27" spans="2:5" ht="14.25">
+      <c r="B27" s="62"/>
       <c r="C27" s="30"/>
       <c r="D27" s="31"/>
       <c r="E27" s="41" t="str">
@@ -6206,7 +5666,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" spans="2:5">
+    <row r="28" spans="2:5" ht="15">
       <c r="B28" s="34"/>
       <c r="C28" s="32"/>
       <c r="D28" s="33"/>
@@ -6215,8 +5675,8 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="2:5">
-      <c r="B29" s="72"/>
+    <row r="29" spans="2:5" ht="14.25">
+      <c r="B29" s="62"/>
       <c r="C29" s="30"/>
       <c r="D29" s="31"/>
       <c r="E29" s="41" t="str">
@@ -6224,7 +5684,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" spans="2:5">
+    <row r="30" spans="2:5" ht="15">
       <c r="B30" s="34"/>
       <c r="C30" s="32"/>
       <c r="D30" s="33"/>
@@ -6233,8 +5693,8 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="14.25" spans="2:5">
-      <c r="B31" s="72"/>
+    <row r="31" spans="2:5" ht="14.25">
+      <c r="B31" s="62"/>
       <c r="C31" s="30"/>
       <c r="D31" s="31"/>
       <c r="E31" s="41" t="str">
@@ -6242,7 +5702,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="15" spans="2:5">
+    <row r="32" spans="2:5" ht="15">
       <c r="B32" s="34"/>
       <c r="C32" s="32"/>
       <c r="D32" s="33"/>
@@ -6251,8 +5711,8 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="2:5">
-      <c r="B33" s="72"/>
+    <row r="33" spans="2:5" ht="14.25">
+      <c r="B33" s="62"/>
       <c r="C33" s="30"/>
       <c r="D33" s="31"/>
       <c r="E33" s="41" t="str">
@@ -6260,7 +5720,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="15" spans="2:5">
+    <row r="34" spans="2:5" ht="15">
       <c r="B34" s="34"/>
       <c r="C34" s="32"/>
       <c r="D34" s="33"/>
@@ -6269,8 +5729,8 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="14.25" spans="2:5">
-      <c r="B35" s="73"/>
+    <row r="35" spans="2:5" ht="14.25">
+      <c r="B35" s="63"/>
       <c r="C35" s="35"/>
       <c r="D35" s="36"/>
       <c r="E35" s="51" t="str">
@@ -6282,36 +5742,33 @@
   <mergeCells count="1">
     <mergeCell ref="G2:H2"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:I26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="B2:I25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="27.625" customWidth="1"/>
     <col min="4" max="4" width="21.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:6">
-      <c r="B2" s="39" t="s">
+    <row r="2" spans="2:9" ht="15">
+      <c r="B2" s="81" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="40"/>
-    </row>
-    <row r="3" ht="14.25" spans="2:6">
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="83"/>
+    </row>
+    <row r="3" spans="2:9" ht="14.25">
       <c r="B3" s="42" t="s">
         <v>23</v>
       </c>
@@ -6328,7 +5785,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:6">
+    <row r="4" spans="2:9" ht="15">
       <c r="B4" s="45" t="s">
         <v>29</v>
       </c>
@@ -6345,26 +5802,25 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:6">
+    <row r="5" spans="2:9" ht="14.25">
       <c r="B5" s="47"/>
       <c r="C5" s="53"/>
       <c r="D5" s="53"/>
-      <c r="E5" s="68"/>
+      <c r="E5" s="59"/>
       <c r="F5" s="48"/>
     </row>
-    <row r="6" ht="15"/>
-    <row r="7" ht="15.75" spans="2:8">
-      <c r="B7" s="54" t="s">
+    <row r="7" spans="2:9" ht="15">
+      <c r="B7" s="102" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="69"/>
-    </row>
-    <row r="8" ht="14.25" spans="2:8">
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="112"/>
+      <c r="G7" s="112"/>
+      <c r="H7" s="103"/>
+    </row>
+    <row r="8" spans="2:9" ht="14.25">
       <c r="B8" s="42" t="s">
         <v>23</v>
       </c>
@@ -6387,7 +5843,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="2:8">
+    <row r="9" spans="2:9" ht="15">
       <c r="B9" s="45" t="s">
         <v>110</v>
       </c>
@@ -6404,7 +5860,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="2:8">
+    <row r="10" spans="2:9" ht="14.25">
       <c r="B10" s="42" t="s">
         <v>30</v>
       </c>
@@ -6425,7 +5881,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="2:8">
+    <row r="11" spans="2:9" ht="15">
       <c r="B11" s="45"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
@@ -6434,7 +5890,7 @@
       <c r="G11" s="44"/>
       <c r="H11" s="46"/>
     </row>
-    <row r="12" ht="14.25" spans="2:8">
+    <row r="12" spans="2:9" ht="14.25">
       <c r="B12" s="42"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
@@ -6443,60 +5899,59 @@
       <c r="G12" s="41"/>
       <c r="H12" s="43"/>
     </row>
-    <row r="13" ht="15.75" spans="2:8">
+    <row r="13" spans="2:9" ht="15">
       <c r="B13" s="49"/>
-      <c r="C13" s="56"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="54"/>
+      <c r="E13" s="54"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="60"/>
       <c r="H13" s="50"/>
     </row>
-    <row r="14" ht="15"/>
-    <row r="15" ht="15.75" spans="2:9">
-      <c r="B15" s="39" t="s">
+    <row r="15" spans="2:9" ht="15">
+      <c r="B15" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="40"/>
-    </row>
-    <row r="16" ht="14.25" spans="2:9">
-      <c r="B16" s="57" t="s">
+      <c r="C15" s="82"/>
+      <c r="D15" s="82"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="83"/>
+    </row>
+    <row r="16" spans="2:9" ht="14.25">
+      <c r="B16" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58" t="s">
+      <c r="D16" s="113"/>
+      <c r="E16" s="56" t="s">
         <v>118</v>
       </c>
-      <c r="F16" s="58" t="s">
+      <c r="F16" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="G16" s="58" t="s">
+      <c r="G16" s="56" t="s">
         <v>107</v>
       </c>
-      <c r="H16" s="58" t="s">
+      <c r="H16" s="56" t="s">
         <v>120</v>
       </c>
-      <c r="I16" s="71" t="s">
+      <c r="I16" s="61" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="17" ht="15" spans="2:9">
+    <row r="17" spans="2:9" ht="15">
       <c r="B17" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C17" s="98" t="s">
+      <c r="C17" s="114" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="107"/>
       <c r="E17" s="33">
         <v>1</v>
       </c>
@@ -6513,12 +5968,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="2:9">
+    <row r="18" spans="2:9" ht="14.25">
       <c r="B18" s="42" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="59"/>
-      <c r="D18" s="59"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="106"/>
       <c r="E18" s="31">
         <v>3</v>
       </c>
@@ -6527,7 +5982,7 @@
       </c>
       <c r="G18" s="31">
         <f t="shared" ref="G18:G21" si="0">PRODUCT(E18:F18)</f>
-        <v>0.3</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="H18" s="31"/>
       <c r="I18" s="43">
@@ -6535,10 +5990,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" ht="15" spans="2:9">
+    <row r="19" spans="2:9" ht="15">
       <c r="B19" s="45"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="107"/>
       <c r="E19" s="33"/>
       <c r="F19" s="33"/>
       <c r="G19" s="33">
@@ -6551,10 +6006,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="14.25" spans="2:9">
+    <row r="20" spans="2:9" ht="14.25">
       <c r="B20" s="42"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="106"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
       <c r="G20" s="31">
@@ -6567,28 +6022,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="15.75" spans="2:9">
+    <row r="21" spans="2:9" ht="15">
       <c r="B21" s="49"/>
-      <c r="C21" s="60"/>
-      <c r="D21" s="60"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56">
+      <c r="C21" s="108"/>
+      <c r="D21" s="108"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H21" s="56"/>
+      <c r="H21" s="54"/>
       <c r="I21" s="50">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="15"/>
-    <row r="23" ht="15.75" spans="2:4">
+    <row r="23" spans="2:9" ht="15">
       <c r="B23" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="61">
+      <c r="C23" s="57">
         <f>SUM(G17:G21,F9:F13,F4:F5)</f>
         <v>13.4</v>
       </c>
@@ -6597,27 +6051,26 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" ht="14.25" spans="2:4">
-      <c r="B24" s="62" t="s">
+    <row r="24" spans="2:9" ht="14.25">
+      <c r="B24" s="58" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="63">
+      <c r="C24" s="109">
         <f>Ligma!C3*10</f>
         <v>160</v>
       </c>
-      <c r="D24" s="64"/>
-    </row>
-    <row r="25" ht="15.75" spans="2:4">
+      <c r="D24" s="110"/>
+    </row>
+    <row r="25" spans="2:9" ht="15">
       <c r="B25" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C25" s="65" t="str">
+      <c r="C25" s="104" t="str">
         <f>IF(C23&gt;D23,"Sobrecarga","Sem Penalidade")</f>
         <v>Sem Penalidade</v>
       </c>
-      <c r="D25" s="66"/>
-    </row>
-    <row r="26" ht="14.25"/>
+      <c r="D25" s="105"/>
+    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="B2:F2"/>
@@ -6625,23 +6078,21 @@
     <mergeCell ref="B15:I15"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:P33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="B2:P33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -6659,8 +6110,7 @@
     <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15" customHeight="1" spans="2:16">
+    <row r="2" spans="2:16" ht="15" customHeight="1">
       <c r="B2" s="28" t="s">
         <v>127</v>
       </c>
@@ -6697,12 +6147,12 @@
       <c r="M2" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="O2" s="39" t="s">
+      <c r="O2" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="P2" s="40"/>
-    </row>
-    <row r="3" ht="14.25" spans="2:16">
+      <c r="P2" s="83"/>
+    </row>
+    <row r="3" spans="2:16" ht="14.25">
       <c r="B3" s="30" t="s">
         <v>136</v>
       </c>
@@ -6718,7 +6168,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G3" s="31"/>
@@ -6744,7 +6194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:16">
+    <row r="4" spans="2:16" ht="15">
       <c r="B4" s="32" t="s">
         <v>141</v>
       </c>
@@ -6760,7 +6210,7 @@
         <v>5</v>
       </c>
       <c r="F4" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G4" s="33"/>
@@ -6786,7 +6236,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:16">
+    <row r="5" spans="2:16" ht="14.25">
       <c r="B5" s="30" t="s">
         <v>143</v>
       </c>
@@ -6802,7 +6252,7 @@
         <v>5</v>
       </c>
       <c r="F5" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G5" s="31"/>
@@ -6828,7 +6278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="2:13">
+    <row r="6" spans="2:16" ht="15">
       <c r="B6" s="32" t="s">
         <v>145</v>
       </c>
@@ -6844,7 +6294,7 @@
         <v>5</v>
       </c>
       <c r="F6" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G6" s="33"/>
@@ -6864,7 +6314,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="2:16">
+    <row r="7" spans="2:16" ht="15.75" customHeight="1">
       <c r="B7" s="30" t="s">
         <v>146</v>
       </c>
@@ -6880,7 +6330,7 @@
         <v>5</v>
       </c>
       <c r="F7" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G7" s="31"/>
@@ -6899,12 +6349,12 @@
       <c r="M7" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="O7" s="39" t="s">
+      <c r="O7" s="81" t="s">
         <v>147</v>
       </c>
-      <c r="P7" s="40"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="2:16">
+      <c r="P7" s="83"/>
+    </row>
+    <row r="8" spans="2:16" ht="15" customHeight="1">
       <c r="B8" s="32" t="s">
         <v>148</v>
       </c>
@@ -6913,22 +6363,22 @@
       </c>
       <c r="D8" s="33">
         <f>VLOOKUP(C8,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="33">
         <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
       <c r="F8" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>9</v>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
       </c>
       <c r="G8" s="33"/>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="J8" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K8" s="33" t="s">
         <v>140</v>
@@ -6947,7 +6397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="2:16">
+    <row r="9" spans="2:16" ht="15">
       <c r="B9" s="30" t="s">
         <v>150</v>
       </c>
@@ -6962,19 +6412,19 @@
         <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F9" s="31">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>9</v>
+      <c r="F9" s="31" t="str">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v/>
       </c>
       <c r="G9" s="31"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="J9" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K9" s="31" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="L9" s="31" t="s">
         <v>139</v>
@@ -6990,7 +6440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="2:16">
+    <row r="10" spans="2:16" ht="15">
       <c r="B10" s="32" t="s">
         <v>152</v>
       </c>
@@ -7006,7 +6456,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G10" s="33"/>
@@ -7033,7 +6483,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="2:16">
+    <row r="11" spans="2:16" ht="15">
       <c r="B11" s="30" t="s">
         <v>153</v>
       </c>
@@ -7049,7 +6499,7 @@
         <v>5</v>
       </c>
       <c r="F11" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G11" s="31"/>
@@ -7073,10 +6523,10 @@
       </c>
       <c r="P11" s="46">
         <f>VLOOKUP(O11,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="2:16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="15">
       <c r="B12" s="32" t="s">
         <v>154</v>
       </c>
@@ -7092,7 +6542,7 @@
         <v>5</v>
       </c>
       <c r="F12" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G12" s="33"/>
@@ -7119,7 +6569,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="15.75" spans="2:16">
+    <row r="13" spans="2:16" ht="15">
       <c r="B13" s="30" t="s">
         <v>156</v>
       </c>
@@ -7135,7 +6585,7 @@
         <v>5</v>
       </c>
       <c r="F13" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G13" s="31"/>
@@ -7162,7 +6612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="2:13">
+    <row r="14" spans="2:16" ht="15">
       <c r="B14" s="32" t="s">
         <v>157</v>
       </c>
@@ -7171,15 +6621,15 @@
       </c>
       <c r="D14" s="33">
         <f>VLOOKUP(C14,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" s="33">
         <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
       <c r="F14" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>9</v>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
       </c>
       <c r="G14" s="33"/>
       <c r="H14" s="33">
@@ -7188,7 +6638,7 @@
       <c r="I14" s="33"/>
       <c r="J14" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K14" s="33" t="s">
         <v>140</v>
@@ -7200,7 +6650,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="2:13">
+    <row r="15" spans="2:16" ht="14.25">
       <c r="B15" s="30" t="s">
         <v>158</v>
       </c>
@@ -7216,7 +6666,7 @@
         <v>5</v>
       </c>
       <c r="F15" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G15" s="31"/>
@@ -7236,7 +6686,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" ht="15" spans="2:13">
+    <row r="16" spans="2:16" ht="15">
       <c r="B16" s="32" t="s">
         <v>159</v>
       </c>
@@ -7252,7 +6702,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G16" s="33"/>
@@ -7272,7 +6722,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="2:13">
+    <row r="17" spans="2:13" ht="14.25">
       <c r="B17" s="30" t="s">
         <v>160</v>
       </c>
@@ -7288,7 +6738,7 @@
         <v>5</v>
       </c>
       <c r="F17" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G17" s="31"/>
@@ -7308,7 +6758,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:13">
+    <row r="18" spans="2:13" ht="15">
       <c r="B18" s="32" t="s">
         <v>161</v>
       </c>
@@ -7317,22 +6767,22 @@
       </c>
       <c r="D18" s="33">
         <f>VLOOKUP(C18,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="33">
         <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
       <c r="F18" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>9</v>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
       </c>
       <c r="G18" s="33"/>
       <c r="H18" s="33"/>
       <c r="I18" s="33"/>
       <c r="J18" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K18" s="33" t="s">
         <v>140</v>
@@ -7344,7 +6794,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="2:13">
+    <row r="19" spans="2:13" ht="14.25">
       <c r="B19" s="30" t="s">
         <v>162</v>
       </c>
@@ -7360,7 +6810,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G19" s="31"/>
@@ -7380,7 +6830,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:13">
+    <row r="20" spans="2:13" ht="15">
       <c r="B20" s="32" t="s">
         <v>163</v>
       </c>
@@ -7396,7 +6846,7 @@
         <v>5</v>
       </c>
       <c r="F20" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G20" s="33"/>
@@ -7416,7 +6866,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="2:13">
+    <row r="21" spans="2:13" ht="14.25">
       <c r="B21" s="30" t="s">
         <v>83</v>
       </c>
@@ -7432,15 +6882,15 @@
         <v>5</v>
       </c>
       <c r="F21" s="31">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>9</v>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
       </c>
       <c r="G21" s="31"/>
       <c r="H21" s="31"/>
       <c r="I21" s="31"/>
       <c r="J21" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K21" s="31" t="s">
         <v>140</v>
@@ -7452,7 +6902,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="22" ht="15" spans="2:13">
+    <row r="22" spans="2:13" ht="15">
       <c r="B22" s="32" t="s">
         <v>164</v>
       </c>
@@ -7461,15 +6911,15 @@
       </c>
       <c r="D22" s="33">
         <f>VLOOKUP(C22,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" s="33">
         <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
       <c r="F22" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>9</v>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
       </c>
       <c r="G22" s="33">
         <v>2</v>
@@ -7478,7 +6928,7 @@
       <c r="I22" s="33"/>
       <c r="J22" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K22" s="33" t="s">
         <v>140</v>
@@ -7490,7 +6940,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="23" ht="14.25" spans="2:13">
+    <row r="23" spans="2:13" ht="14.25">
       <c r="B23" s="30" t="s">
         <v>165</v>
       </c>
@@ -7499,14 +6949,14 @@
       </c>
       <c r="D23" s="31">
         <f>VLOOKUP(C23,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" s="31">
         <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
       <c r="F23" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G23" s="31"/>
@@ -7514,7 +6964,7 @@
       <c r="I23" s="31"/>
       <c r="J23" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K23" s="31" t="s">
         <v>138</v>
@@ -7526,7 +6976,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="24" ht="15" spans="2:13">
+    <row r="24" spans="2:13" ht="15">
       <c r="B24" s="32" t="s">
         <v>166</v>
       </c>
@@ -7535,22 +6985,22 @@
       </c>
       <c r="D24" s="33">
         <f>VLOOKUP(C24,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" s="33">
         <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
       <c r="F24" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>9</v>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
       </c>
       <c r="G24" s="33"/>
       <c r="H24" s="33"/>
       <c r="I24" s="33"/>
       <c r="J24" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K24" s="33" t="s">
         <v>140</v>
@@ -7562,7 +7012,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="2:13">
+    <row r="25" spans="2:13" ht="14.25">
       <c r="B25" s="30" t="s">
         <v>167</v>
       </c>
@@ -7571,22 +7021,22 @@
       </c>
       <c r="D25" s="31">
         <f>VLOOKUP(C25,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" s="31">
         <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
       <c r="F25" s="31">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>9</v>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
       <c r="J25" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K25" s="31" t="s">
         <v>140</v>
@@ -7598,7 +7048,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="26" ht="15" spans="2:13">
+    <row r="26" spans="2:13" ht="15">
       <c r="B26" s="34" t="s">
         <v>168</v>
       </c>
@@ -7607,22 +7057,22 @@
       </c>
       <c r="D26" s="33">
         <f>VLOOKUP(C26,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="33">
         <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
       <c r="F26" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>9</v>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
       </c>
       <c r="G26" s="33"/>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
       <c r="J26" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="K26" s="33" t="s">
         <v>140</v>
@@ -7634,7 +7084,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" ht="14.25" spans="2:13">
+    <row r="27" spans="2:13" ht="14.25">
       <c r="B27" s="30" t="s">
         <v>169</v>
       </c>
@@ -7650,8 +7100,8 @@
         <v>5</v>
       </c>
       <c r="F27" s="31">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>9</v>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
       </c>
       <c r="G27" s="31">
         <v>2</v>
@@ -7660,7 +7110,7 @@
       <c r="I27" s="31"/>
       <c r="J27" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K27" s="31" t="s">
         <v>140</v>
@@ -7672,7 +7122,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="28" ht="15" spans="2:13">
+    <row r="28" spans="2:13" ht="15">
       <c r="B28" s="32" t="s">
         <v>170</v>
       </c>
@@ -7688,7 +7138,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G28" s="33"/>
@@ -7708,7 +7158,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="2:13">
+    <row r="29" spans="2:13" ht="14.25">
       <c r="B29" s="30" t="s">
         <v>171</v>
       </c>
@@ -7723,19 +7173,19 @@
         <f>ROUNDDOWN(Ligma!$G$2/2,0)</f>
         <v>5</v>
       </c>
-      <c r="F29" s="31" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v/>
+      <c r="F29" s="31">
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
       </c>
       <c r="G29" s="31"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="J29" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K29" s="31" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L29" s="31" t="s">
         <v>139</v>
@@ -7744,7 +7194,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="30" ht="15" spans="2:13">
+    <row r="30" spans="2:13" ht="15">
       <c r="B30" s="32" t="s">
         <v>172</v>
       </c>
@@ -7760,15 +7210,15 @@
         <v>5</v>
       </c>
       <c r="F30" s="33">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>9</v>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
       </c>
       <c r="G30" s="33"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
       <c r="J30" s="33">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="K30" s="33" t="s">
         <v>140</v>
@@ -7780,7 +7230,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="31" ht="14.25" spans="2:13">
+    <row r="31" spans="2:13" ht="14.25">
       <c r="B31" s="30" t="s">
         <v>173</v>
       </c>
@@ -7796,15 +7246,15 @@
         <v>5</v>
       </c>
       <c r="F31" s="31">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>9</v>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
       </c>
       <c r="G31" s="31"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="J31" s="31">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K31" s="31" t="s">
         <v>140</v>
@@ -7816,7 +7266,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="32" ht="15" spans="2:13">
+    <row r="32" spans="2:13" ht="15">
       <c r="B32" s="32" t="s">
         <v>174</v>
       </c>
@@ -7832,7 +7282,7 @@
         <v>5</v>
       </c>
       <c r="F32" s="33" t="str">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
         <v/>
       </c>
       <c r="G32" s="33"/>
@@ -7852,7 +7302,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="2:13">
+    <row r="33" spans="2:13" ht="14.25">
       <c r="B33" s="35" t="s">
         <v>175</v>
       </c>
@@ -7868,15 +7318,15 @@
         <v>5</v>
       </c>
       <c r="F33" s="36">
-        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$2:$K$22,2,TRUE),"")</f>
-        <v>9</v>
+        <f>IF(Tabela1[[#This Row],[Treinada?]]="sim",VLOOKUP(Ligma!$G$2,'uns dados aí'!$E$2:$F$4,2,TRUE),"")</f>
+        <v>4</v>
       </c>
       <c r="G33" s="36"/>
       <c r="H33" s="36"/>
       <c r="I33" s="36"/>
       <c r="J33" s="36">
         <f>SUM(Tabela1[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela1[[#This Row],[Penalidade de Armadura?]]="sim",Ligma!$D$16,0)</f>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K33" s="36" t="s">
         <v>140</v>
@@ -7893,9 +7343,8 @@
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="O7:P7"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -7903,9 +7352,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:P33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="B2:P33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -7923,8 +7371,7 @@
     <col min="15" max="15" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15" customHeight="1" spans="2:16">
+    <row r="2" spans="2:16" ht="15" customHeight="1">
       <c r="B2" s="28" t="s">
         <v>127</v>
       </c>
@@ -7961,12 +7408,12 @@
       <c r="M2" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="O2" s="39" t="s">
+      <c r="O2" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="P2" s="40"/>
-    </row>
-    <row r="3" ht="14.25" spans="2:16">
+      <c r="P2" s="83"/>
+    </row>
+    <row r="3" spans="2:16" ht="14.25">
       <c r="B3" s="30" t="s">
         <v>136</v>
       </c>
@@ -8008,7 +7455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="15" spans="2:16">
+    <row r="4" spans="2:16" ht="15">
       <c r="B4" s="32" t="s">
         <v>141</v>
       </c>
@@ -8050,7 +7497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:16">
+    <row r="5" spans="2:16" ht="14.25">
       <c r="B5" s="30" t="s">
         <v>143</v>
       </c>
@@ -8092,7 +7539,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="2:13">
+    <row r="6" spans="2:16" ht="15">
       <c r="B6" s="32" t="s">
         <v>145</v>
       </c>
@@ -8128,7 +7575,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="2:16">
+    <row r="7" spans="2:16" ht="15.75" customHeight="1">
       <c r="B7" s="30" t="s">
         <v>146</v>
       </c>
@@ -8163,12 +7610,12 @@
       <c r="M7" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="O7" s="39" t="s">
+      <c r="O7" s="81" t="s">
         <v>147</v>
       </c>
-      <c r="P7" s="40"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" spans="2:16">
+      <c r="P7" s="83"/>
+    </row>
+    <row r="8" spans="2:16" ht="15" customHeight="1">
       <c r="B8" s="32" t="s">
         <v>148</v>
       </c>
@@ -8177,7 +7624,7 @@
       </c>
       <c r="D8" s="33">
         <f>VLOOKUP(C8,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="33">
         <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
@@ -8192,7 +7639,7 @@
       <c r="I8" s="33"/>
       <c r="J8" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C4,0)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K8" s="33" t="s">
         <v>140</v>
@@ -8211,7 +7658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="2:16">
+    <row r="9" spans="2:16" ht="15">
       <c r="B9" s="30" t="s">
         <v>150</v>
       </c>
@@ -8254,7 +7701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="2:16">
+    <row r="10" spans="2:16" ht="15">
       <c r="B10" s="32" t="s">
         <v>152</v>
       </c>
@@ -8297,7 +7744,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="2:16">
+    <row r="11" spans="2:16" ht="15">
       <c r="B11" s="30" t="s">
         <v>153</v>
       </c>
@@ -8337,10 +7784,10 @@
       </c>
       <c r="P11" s="46">
         <f>VLOOKUP(O11,'uns dados aí'!$B$16:$E$22,4,FALSE)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" ht="15" spans="2:16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" ht="15">
       <c r="B12" s="32" t="s">
         <v>154</v>
       </c>
@@ -8383,7 +7830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="15.75" spans="2:16">
+    <row r="13" spans="2:16" ht="15">
       <c r="B13" s="30" t="s">
         <v>156</v>
       </c>
@@ -8426,7 +7873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="2:13">
+    <row r="14" spans="2:16" ht="15">
       <c r="B14" s="32" t="s">
         <v>157</v>
       </c>
@@ -8435,7 +7882,7 @@
       </c>
       <c r="D14" s="33">
         <f>VLOOKUP(C14,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" s="33">
         <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
@@ -8452,7 +7899,7 @@
       <c r="I14" s="33"/>
       <c r="J14" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C10,0)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K14" s="33" t="s">
         <v>140</v>
@@ -8464,7 +7911,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="2:13">
+    <row r="15" spans="2:16" ht="14.25">
       <c r="B15" s="30" t="s">
         <v>158</v>
       </c>
@@ -8500,7 +7947,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="16" ht="15" spans="2:13">
+    <row r="16" spans="2:16" ht="15">
       <c r="B16" s="32" t="s">
         <v>159</v>
       </c>
@@ -8536,7 +7983,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="2:13">
+    <row r="17" spans="2:13" ht="14.25">
       <c r="B17" s="30" t="s">
         <v>160</v>
       </c>
@@ -8572,7 +8019,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:13">
+    <row r="18" spans="2:13" ht="15">
       <c r="B18" s="32" t="s">
         <v>161</v>
       </c>
@@ -8581,7 +8028,7 @@
       </c>
       <c r="D18" s="33">
         <f>VLOOKUP(C18,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="33">
         <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
@@ -8596,7 +8043,7 @@
       <c r="I18" s="33"/>
       <c r="J18" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C14,0)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K18" s="33" t="s">
         <v>140</v>
@@ -8608,7 +8055,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="2:13">
+    <row r="19" spans="2:13" ht="14.25">
       <c r="B19" s="30" t="s">
         <v>162</v>
       </c>
@@ -8644,7 +8091,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:13">
+    <row r="20" spans="2:13" ht="15">
       <c r="B20" s="32" t="s">
         <v>163</v>
       </c>
@@ -8680,7 +8127,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="2:13">
+    <row r="21" spans="2:13" ht="14.25">
       <c r="B21" s="30" t="s">
         <v>83</v>
       </c>
@@ -8716,7 +8163,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="22" ht="15" spans="2:13">
+    <row r="22" spans="2:13" ht="15">
       <c r="B22" s="32" t="s">
         <v>164</v>
       </c>
@@ -8725,7 +8172,7 @@
       </c>
       <c r="D22" s="33">
         <f>VLOOKUP(C22,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E22" s="33">
         <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
@@ -8742,7 +8189,7 @@
       <c r="I22" s="33"/>
       <c r="J22" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C18,0)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K22" s="33" t="s">
         <v>140</v>
@@ -8754,7 +8201,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="23" ht="14.25" spans="2:13">
+    <row r="23" spans="2:13" ht="14.25">
       <c r="B23" s="30" t="s">
         <v>165</v>
       </c>
@@ -8763,7 +8210,7 @@
       </c>
       <c r="D23" s="31">
         <f>VLOOKUP(C23,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E23" s="31">
         <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
@@ -8778,7 +8225,7 @@
       <c r="I23" s="31"/>
       <c r="J23" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C19,0)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K23" s="31" t="s">
         <v>138</v>
@@ -8790,7 +8237,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="24" ht="15" spans="2:13">
+    <row r="24" spans="2:13" ht="15">
       <c r="B24" s="32" t="s">
         <v>166</v>
       </c>
@@ -8799,7 +8246,7 @@
       </c>
       <c r="D24" s="33">
         <f>VLOOKUP(C24,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" s="33">
         <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
@@ -8814,7 +8261,7 @@
       <c r="I24" s="33"/>
       <c r="J24" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C20,0)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K24" s="33" t="s">
         <v>140</v>
@@ -8826,7 +8273,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="2:13">
+    <row r="25" spans="2:13" ht="14.25">
       <c r="B25" s="30" t="s">
         <v>167</v>
       </c>
@@ -8835,7 +8282,7 @@
       </c>
       <c r="D25" s="31">
         <f>VLOOKUP(C25,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" s="31">
         <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
@@ -8850,7 +8297,7 @@
       <c r="I25" s="31"/>
       <c r="J25" s="31">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C21,0)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K25" s="31" t="s">
         <v>140</v>
@@ -8862,7 +8309,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="26" ht="15" spans="2:13">
+    <row r="26" spans="2:13" ht="15">
       <c r="B26" s="34" t="s">
         <v>168</v>
       </c>
@@ -8871,7 +8318,7 @@
       </c>
       <c r="D26" s="33">
         <f>VLOOKUP(C26,Ligma!$B$3:$D$8,3,FALSE)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="33">
         <f>VLOOKUP(Ligma!$G$2,'uns dados aí'!$I$3:$K$22,2,FALSE)</f>
@@ -8886,7 +8333,7 @@
       <c r="I26" s="33"/>
       <c r="J26" s="33">
         <f>SUM(Tabela14[[#This Row],[MOD]:[Bônus Habilidade]])-IF(Tabela14[[#This Row],[Penalidade de Armadura?]]="sim",Poderes!C22,0)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K26" s="33" t="s">
         <v>140</v>
@@ -8898,7 +8345,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" ht="14.25" spans="2:13">
+    <row r="27" spans="2:13" ht="14.25">
       <c r="B27" s="30" t="s">
         <v>169</v>
       </c>
@@ -8936,7 +8383,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="28" ht="15" spans="2:13">
+    <row r="28" spans="2:13" ht="15">
       <c r="B28" s="32" t="s">
         <v>170</v>
       </c>
@@ -8972,7 +8419,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="2:13">
+    <row r="29" spans="2:13" ht="14.25">
       <c r="B29" s="30" t="s">
         <v>171</v>
       </c>
@@ -9008,7 +8455,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="30" ht="15" spans="2:13">
+    <row r="30" spans="2:13" ht="15">
       <c r="B30" s="32" t="s">
         <v>172</v>
       </c>
@@ -9044,7 +8491,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="31" ht="14.25" spans="2:13">
+    <row r="31" spans="2:13" ht="14.25">
       <c r="B31" s="30" t="s">
         <v>173</v>
       </c>
@@ -9080,7 +8527,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="32" ht="15" spans="2:13">
+    <row r="32" spans="2:13" ht="15">
       <c r="B32" s="32" t="s">
         <v>174</v>
       </c>
@@ -9116,7 +8563,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="2:13">
+    <row r="33" spans="2:13" ht="14.25">
       <c r="B33" s="35" t="s">
         <v>175</v>
       </c>
@@ -9157,9 +8604,8 @@
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="O7:P7"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -9167,9 +8613,8 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:N23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="B2:N22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="10.25" customWidth="1"/>
@@ -9179,12 +8624,11 @@
     <col min="11" max="11" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25"/>
-    <row r="2" ht="15.75" spans="2:14">
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="2:14" ht="15">
+      <c r="B2" s="115" t="s">
         <v>176</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="116"/>
       <c r="E2" s="1">
         <v>1</v>
       </c>
@@ -9211,7 +8655,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="2:14">
+    <row r="3" spans="2:14" ht="14.25">
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -9244,7 +8688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" ht="15.75" spans="2:14">
+    <row r="4" spans="2:14" ht="15">
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -9277,7 +8721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="15" spans="2:11">
+    <row r="5" spans="2:14" ht="14.25">
       <c r="B5" s="3" t="s">
         <v>10</v>
       </c>
@@ -9298,7 +8742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="15" spans="2:11">
+    <row r="6" spans="2:14" ht="15">
       <c r="B6" s="5" t="s">
         <v>12</v>
       </c>
@@ -9319,7 +8763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="2:11">
+    <row r="7" spans="2:14" ht="14.25">
       <c r="B7" s="3" t="s">
         <v>14</v>
       </c>
@@ -9340,7 +8784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="2:11">
+    <row r="8" spans="2:14" ht="15">
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
@@ -9361,7 +8805,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="15" spans="8:11">
+    <row r="9" spans="2:14" ht="14.25">
       <c r="H9" s="17">
         <v>21000</v>
       </c>
@@ -9376,7 +8820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" ht="15" spans="8:11">
+    <row r="10" spans="2:14" ht="15">
       <c r="H10" s="16">
         <v>28000</v>
       </c>
@@ -9391,7 +8835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="15" spans="8:11">
+    <row r="11" spans="2:14" ht="14.25">
       <c r="H11" s="17">
         <v>36000</v>
       </c>
@@ -9406,7 +8850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" ht="15.75" spans="2:11">
+    <row r="12" spans="2:14" ht="15">
       <c r="B12" s="1" t="s">
         <v>184</v>
       </c>
@@ -9428,7 +8872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="2:11">
+    <row r="13" spans="2:14" ht="14.25">
       <c r="B13" s="3" t="s">
         <v>185</v>
       </c>
@@ -9450,7 +8894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" ht="15.75" spans="2:11">
+    <row r="14" spans="2:14" ht="15">
       <c r="B14" s="7"/>
       <c r="C14" s="8"/>
       <c r="H14" s="16">
@@ -9467,7 +8911,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="15.75" spans="8:11">
+    <row r="15" spans="2:14" ht="14.25">
       <c r="H15" s="17">
         <v>78000</v>
       </c>
@@ -9482,7 +8926,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" ht="15.75" spans="2:11">
+    <row r="16" spans="2:14" ht="15">
       <c r="B16" s="9" t="s">
         <v>128</v>
       </c>
@@ -9509,7 +8953,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" ht="15" spans="2:11">
+    <row r="17" spans="2:11" ht="15">
       <c r="B17" s="5" t="s">
         <v>4</v>
       </c>
@@ -9535,7 +8979,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" ht="15" spans="2:11">
+    <row r="18" spans="2:11" ht="15">
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -9561,7 +9005,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" ht="15" spans="2:11">
+    <row r="19" spans="2:11" ht="15">
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
@@ -9587,19 +9031,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" ht="15" spans="2:11">
+    <row r="20" spans="2:11" ht="15">
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C20" s="12">
         <v>4</v>
       </c>
-      <c r="D20" s="12">
-        <v>2</v>
-      </c>
+      <c r="D20" s="12"/>
       <c r="E20" s="4">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H20" s="16">
         <v>153000</v>
@@ -9615,7 +9057,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" ht="15" spans="2:11">
+    <row r="21" spans="2:11" ht="15">
       <c r="B21" s="5" t="s">
         <v>14</v>
       </c>
@@ -9643,7 +9085,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" ht="15.75" spans="2:11">
+    <row r="22" spans="2:11" ht="15">
       <c r="B22" s="13" t="s">
         <v>16</v>
       </c>
@@ -9669,12 +9111,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" ht="14.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <headerFooter/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>